--- a/output.xlsx
+++ b/output.xlsx
@@ -446,34 +446,34 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>69.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="C2">
-        <v>69.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D2">
-        <v>69.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E2">
-        <v>69.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F2">
-        <v>69.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G2">
-        <v>69.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H2">
-        <v>69.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I2">
-        <v>69.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J2">
-        <v>69.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K2">
-        <v>69.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -779,7 +779,7 @@
         <v>69.59999999999999</v>
       </c>
       <c r="H11">
-        <v>92.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I11">
         <v>69.59999999999999</v>
@@ -814,7 +814,7 @@
         <v>69.59999999999999</v>
       </c>
       <c r="H12">
-        <v>92.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I12">
         <v>69.59999999999999</v>
@@ -840,7 +840,7 @@
         <v>69.59999999999999</v>
       </c>
       <c r="E13">
-        <v>69.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F13">
         <v>69.59999999999999</v>
@@ -849,7 +849,7 @@
         <v>69.59999999999999</v>
       </c>
       <c r="H13">
-        <v>92.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I13">
         <v>69.59999999999999</v>
@@ -875,7 +875,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="E14">
-        <v>92.09999999999999</v>
+        <v>114.6</v>
       </c>
       <c r="F14">
         <v>92.09999999999999</v>
@@ -884,7 +884,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="H14">
-        <v>114.6</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I14">
         <v>92.09999999999999</v>
@@ -910,7 +910,7 @@
         <v>114.6</v>
       </c>
       <c r="E15">
-        <v>114.6</v>
+        <v>137.1</v>
       </c>
       <c r="F15">
         <v>114.6</v>
@@ -919,7 +919,7 @@
         <v>114.6</v>
       </c>
       <c r="H15">
-        <v>137.1</v>
+        <v>114.6</v>
       </c>
       <c r="I15">
         <v>114.6</v>
@@ -945,7 +945,7 @@
         <v>137.1</v>
       </c>
       <c r="E16">
-        <v>137.1</v>
+        <v>159.6</v>
       </c>
       <c r="F16">
         <v>137.1</v>
@@ -954,7 +954,7 @@
         <v>137.1</v>
       </c>
       <c r="H16">
-        <v>159.6</v>
+        <v>137.1</v>
       </c>
       <c r="I16">
         <v>137.1</v>
@@ -980,7 +980,7 @@
         <v>159.6</v>
       </c>
       <c r="E17">
-        <v>159.6</v>
+        <v>182.1</v>
       </c>
       <c r="F17">
         <v>159.6</v>
@@ -989,7 +989,7 @@
         <v>159.6</v>
       </c>
       <c r="H17">
-        <v>182.1</v>
+        <v>159.6</v>
       </c>
       <c r="I17">
         <v>159.6</v>
@@ -1015,7 +1015,7 @@
         <v>182.1</v>
       </c>
       <c r="E18">
-        <v>182.1</v>
+        <v>204.6</v>
       </c>
       <c r="F18">
         <v>182.1</v>
@@ -1024,7 +1024,7 @@
         <v>182.1</v>
       </c>
       <c r="H18">
-        <v>204.6</v>
+        <v>182.1</v>
       </c>
       <c r="I18">
         <v>182.1</v>
@@ -1050,7 +1050,7 @@
         <v>204.6</v>
       </c>
       <c r="E19">
-        <v>204.6</v>
+        <v>227.1</v>
       </c>
       <c r="F19">
         <v>204.6</v>
@@ -1059,7 +1059,7 @@
         <v>204.6</v>
       </c>
       <c r="H19">
-        <v>227.1</v>
+        <v>204.6</v>
       </c>
       <c r="I19">
         <v>204.6</v>
@@ -1085,7 +1085,7 @@
         <v>227.1</v>
       </c>
       <c r="E20">
-        <v>227.1</v>
+        <v>249.6</v>
       </c>
       <c r="F20">
         <v>227.1</v>
@@ -1094,7 +1094,7 @@
         <v>227.1</v>
       </c>
       <c r="H20">
-        <v>249.6</v>
+        <v>227.1</v>
       </c>
       <c r="I20">
         <v>227.1</v>
@@ -1120,7 +1120,7 @@
         <v>249.6</v>
       </c>
       <c r="E21">
-        <v>249.6</v>
+        <v>272.1</v>
       </c>
       <c r="F21">
         <v>249.6</v>
@@ -1129,7 +1129,7 @@
         <v>249.6</v>
       </c>
       <c r="H21">
-        <v>272.1</v>
+        <v>249.6</v>
       </c>
       <c r="I21">
         <v>249.6</v>
@@ -1146,28 +1146,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>249.6</v>
+        <v>272.1</v>
       </c>
       <c r="C22">
         <v>272.1</v>
       </c>
       <c r="D22">
+        <v>249.6</v>
+      </c>
+      <c r="E22">
+        <v>294.6</v>
+      </c>
+      <c r="F22">
+        <v>249.6</v>
+      </c>
+      <c r="G22">
+        <v>249.6</v>
+      </c>
+      <c r="H22">
         <v>272.1</v>
       </c>
-      <c r="E22">
-        <v>272.1</v>
-      </c>
-      <c r="F22">
-        <v>272.1</v>
-      </c>
-      <c r="G22">
-        <v>272.1</v>
-      </c>
-      <c r="H22">
-        <v>294.6</v>
-      </c>
       <c r="I22">
-        <v>272.1</v>
+        <v>249.6</v>
       </c>
       <c r="J22">
         <v>272.1</v>
@@ -1181,16 +1181,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>272.1</v>
+        <v>294.6</v>
       </c>
       <c r="C23">
         <v>294.6</v>
       </c>
       <c r="D23">
-        <v>294.5999973015</v>
+        <v>272.1</v>
       </c>
       <c r="E23">
-        <v>272.1</v>
+        <v>290.7</v>
       </c>
       <c r="F23">
         <v>272.1</v>
@@ -1199,7 +1199,7 @@
         <v>272.1</v>
       </c>
       <c r="H23">
-        <v>290.7</v>
+        <v>294.6</v>
       </c>
       <c r="I23">
         <v>272.1</v>
@@ -1208,7 +1208,7 @@
         <v>294.6</v>
       </c>
       <c r="K23">
-        <v>294.6</v>
+        <v>272.1</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1216,34 +1216,34 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>272.1</v>
+        <v>294.6</v>
       </c>
       <c r="C24">
         <v>317.1</v>
       </c>
       <c r="D24">
-        <v>294.59999730075</v>
+        <v>272.1</v>
       </c>
       <c r="E24">
-        <v>294.6</v>
+        <v>286.8</v>
       </c>
       <c r="F24">
-        <v>294.6</v>
+        <v>272.1</v>
       </c>
       <c r="G24">
         <v>272.1</v>
       </c>
       <c r="H24">
-        <v>286.8</v>
+        <v>317.1</v>
       </c>
       <c r="I24">
-        <v>294.6</v>
+        <v>272.1</v>
       </c>
       <c r="J24">
-        <v>294.6</v>
+        <v>317.1</v>
       </c>
       <c r="K24">
-        <v>317.1</v>
+        <v>272.1</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1251,16 +1251,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>272.1</v>
+        <v>290.7</v>
       </c>
       <c r="C25">
         <v>317.1</v>
       </c>
       <c r="D25">
-        <v>294.5999973015</v>
+        <v>272.1</v>
       </c>
       <c r="E25">
-        <v>317.1</v>
+        <v>282.9</v>
       </c>
       <c r="F25">
         <v>294.6</v>
@@ -1269,16 +1269,16 @@
         <v>272.1</v>
       </c>
       <c r="H25">
-        <v>282.9</v>
+        <v>313.2</v>
       </c>
       <c r="I25">
         <v>294.6</v>
       </c>
       <c r="J25">
-        <v>290.7</v>
+        <v>317.1</v>
       </c>
       <c r="K25">
-        <v>313.2</v>
+        <v>294.6</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1286,16 +1286,16 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>272.1</v>
+        <v>286.8</v>
       </c>
       <c r="C26">
         <v>317.1</v>
       </c>
       <c r="D26">
-        <v>294.5999973015</v>
+        <v>272.1</v>
       </c>
       <c r="E26">
-        <v>317.1</v>
+        <v>279</v>
       </c>
       <c r="F26">
         <v>294.6</v>
@@ -1304,16 +1304,16 @@
         <v>272.1</v>
       </c>
       <c r="H26">
-        <v>279</v>
+        <v>309.3</v>
       </c>
       <c r="I26">
         <v>294.6</v>
       </c>
       <c r="J26">
-        <v>286.8</v>
+        <v>317.1</v>
       </c>
       <c r="K26">
-        <v>309.3</v>
+        <v>294.6</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1321,16 +1321,16 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>272.1</v>
+        <v>282.9</v>
       </c>
       <c r="C27">
         <v>317.1</v>
       </c>
       <c r="D27">
-        <v>294.5999973015</v>
+        <v>272.1</v>
       </c>
       <c r="E27">
-        <v>317.1</v>
+        <v>275.1</v>
       </c>
       <c r="F27">
         <v>294.6</v>
@@ -1339,16 +1339,16 @@
         <v>272.1</v>
       </c>
       <c r="H27">
-        <v>275.1</v>
+        <v>305.4</v>
       </c>
       <c r="I27">
         <v>294.6</v>
       </c>
       <c r="J27">
-        <v>282.9</v>
+        <v>317.1</v>
       </c>
       <c r="K27">
-        <v>305.4</v>
+        <v>294.6</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1356,16 +1356,16 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>272.1</v>
+        <v>279</v>
       </c>
       <c r="C28">
         <v>317.1</v>
       </c>
       <c r="D28">
-        <v>294.59999730075</v>
+        <v>272.1</v>
       </c>
       <c r="E28">
-        <v>317.1</v>
+        <v>271.2</v>
       </c>
       <c r="F28">
         <v>294.6</v>
@@ -1374,16 +1374,16 @@
         <v>272.1</v>
       </c>
       <c r="H28">
-        <v>271.2</v>
+        <v>301.5</v>
       </c>
       <c r="I28">
         <v>294.6</v>
       </c>
       <c r="J28">
-        <v>279</v>
+        <v>317.1</v>
       </c>
       <c r="K28">
-        <v>301.5</v>
+        <v>294.6</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1391,16 +1391,16 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>272.1</v>
+        <v>275.1</v>
       </c>
       <c r="C29">
         <v>317.1</v>
       </c>
       <c r="D29">
-        <v>290.69999730075</v>
+        <v>272.1</v>
       </c>
       <c r="E29">
-        <v>313.2</v>
+        <v>267.3</v>
       </c>
       <c r="F29">
         <v>294.6</v>
@@ -1409,16 +1409,16 @@
         <v>272.1</v>
       </c>
       <c r="H29">
-        <v>267.3</v>
+        <v>297.6</v>
       </c>
       <c r="I29">
         <v>290.7</v>
       </c>
       <c r="J29">
-        <v>275.1</v>
+        <v>313.2</v>
       </c>
       <c r="K29">
-        <v>297.6</v>
+        <v>290.7</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1426,16 +1426,16 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>272.1</v>
+        <v>271.2</v>
       </c>
       <c r="C30">
         <v>317.1</v>
       </c>
       <c r="D30">
-        <v>286.79999730075</v>
+        <v>272.1</v>
       </c>
       <c r="E30">
-        <v>309.3</v>
+        <v>263.4</v>
       </c>
       <c r="F30">
         <v>294.6</v>
@@ -1444,16 +1444,16 @@
         <v>272.1</v>
       </c>
       <c r="H30">
-        <v>263.4</v>
+        <v>293.7</v>
       </c>
       <c r="I30">
         <v>286.8</v>
       </c>
       <c r="J30">
-        <v>271.2</v>
+        <v>309.3</v>
       </c>
       <c r="K30">
-        <v>293.7</v>
+        <v>286.8</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1461,16 +1461,16 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>272.1</v>
+        <v>267.3</v>
       </c>
       <c r="C31">
         <v>317.1</v>
       </c>
       <c r="D31">
-        <v>282.8999973007499</v>
+        <v>272.1</v>
       </c>
       <c r="E31">
-        <v>305.4</v>
+        <v>259.5</v>
       </c>
       <c r="F31">
         <v>290.7</v>
@@ -1479,16 +1479,16 @@
         <v>272.1</v>
       </c>
       <c r="H31">
-        <v>259.5</v>
+        <v>289.8</v>
       </c>
       <c r="I31">
         <v>282.9</v>
       </c>
       <c r="J31">
-        <v>267.3</v>
+        <v>305.4</v>
       </c>
       <c r="K31">
-        <v>289.8</v>
+        <v>282.9</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1496,34 +1496,34 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>268.2</v>
+        <v>263.4</v>
       </c>
       <c r="C32">
         <v>313.2</v>
       </c>
       <c r="D32">
-        <v>278.99999730075</v>
+        <v>272.1</v>
       </c>
       <c r="E32">
-        <v>301.5</v>
+        <v>255.6</v>
       </c>
       <c r="F32">
         <v>286.8</v>
       </c>
       <c r="G32">
-        <v>272.1</v>
+        <v>268.2</v>
       </c>
       <c r="H32">
-        <v>255.6</v>
+        <v>285.9</v>
       </c>
       <c r="I32">
         <v>279</v>
       </c>
       <c r="J32">
-        <v>263.4</v>
+        <v>301.5</v>
       </c>
       <c r="K32">
-        <v>285.9</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1531,34 +1531,34 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>264.3</v>
+        <v>259.5</v>
       </c>
       <c r="C33">
         <v>309.3</v>
       </c>
       <c r="D33">
-        <v>275.09999730075</v>
+        <v>272.1</v>
       </c>
       <c r="E33">
-        <v>297.6</v>
+        <v>251.7</v>
       </c>
       <c r="F33">
         <v>282.9</v>
       </c>
       <c r="G33">
-        <v>272.1</v>
+        <v>264.3</v>
       </c>
       <c r="H33">
-        <v>251.7</v>
+        <v>282</v>
       </c>
       <c r="I33">
         <v>275.1</v>
       </c>
       <c r="J33">
-        <v>259.5</v>
+        <v>297.6</v>
       </c>
       <c r="K33">
-        <v>282</v>
+        <v>275.1</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1566,34 +1566,34 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>260.4</v>
+        <v>255.6</v>
       </c>
       <c r="C34">
         <v>305.4</v>
       </c>
       <c r="D34">
-        <v>271.1999973005999</v>
+        <v>272.1</v>
       </c>
       <c r="E34">
-        <v>293.7</v>
+        <v>247.8</v>
       </c>
       <c r="F34">
         <v>279</v>
       </c>
       <c r="G34">
-        <v>272.1</v>
+        <v>260.4</v>
       </c>
       <c r="H34">
-        <v>247.8</v>
+        <v>278.1</v>
       </c>
       <c r="I34">
         <v>271.2</v>
       </c>
       <c r="J34">
-        <v>255.6</v>
+        <v>293.7</v>
       </c>
       <c r="K34">
-        <v>278.1</v>
+        <v>271.2</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1601,34 +1601,34 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>256.5</v>
+        <v>251.7</v>
       </c>
       <c r="C35">
         <v>301.5</v>
       </c>
       <c r="D35">
-        <v>267.2999973006</v>
+        <v>268.2</v>
       </c>
       <c r="E35">
-        <v>289.8</v>
+        <v>243.9</v>
       </c>
       <c r="F35">
         <v>275.1</v>
       </c>
       <c r="G35">
-        <v>268.2</v>
+        <v>256.5</v>
       </c>
       <c r="H35">
-        <v>243.9</v>
+        <v>274.2</v>
       </c>
       <c r="I35">
         <v>267.3</v>
       </c>
       <c r="J35">
-        <v>251.7</v>
+        <v>289.8</v>
       </c>
       <c r="K35">
-        <v>274.2</v>
+        <v>267.3</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1636,34 +1636,34 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>252.6</v>
+        <v>247.8</v>
       </c>
       <c r="C36">
         <v>297.6</v>
       </c>
       <c r="D36">
-        <v>263.3999973006</v>
+        <v>264.3</v>
       </c>
       <c r="E36">
-        <v>285.9</v>
+        <v>240</v>
       </c>
       <c r="F36">
         <v>271.2</v>
       </c>
       <c r="G36">
-        <v>264.3</v>
+        <v>252.6</v>
       </c>
       <c r="H36">
-        <v>240</v>
+        <v>270.3</v>
       </c>
       <c r="I36">
         <v>263.4</v>
       </c>
       <c r="J36">
-        <v>247.8</v>
+        <v>285.9</v>
       </c>
       <c r="K36">
-        <v>270.3</v>
+        <v>263.4</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1671,34 +1671,34 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>248.7</v>
+        <v>243.9</v>
       </c>
       <c r="C37">
         <v>293.7</v>
       </c>
       <c r="D37">
-        <v>259.4999973005999</v>
+        <v>260.4</v>
       </c>
       <c r="E37">
-        <v>282</v>
+        <v>236.1</v>
       </c>
       <c r="F37">
         <v>267.3</v>
       </c>
       <c r="G37">
-        <v>260.4</v>
+        <v>248.7</v>
       </c>
       <c r="H37">
-        <v>236.1</v>
+        <v>266.4</v>
       </c>
       <c r="I37">
         <v>259.5</v>
       </c>
       <c r="J37">
-        <v>243.9</v>
+        <v>282</v>
       </c>
       <c r="K37">
-        <v>266.4</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1706,34 +1706,34 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>244.8</v>
+        <v>240</v>
       </c>
       <c r="C38">
         <v>289.8</v>
       </c>
       <c r="D38">
-        <v>255.5999973006</v>
+        <v>256.5</v>
       </c>
       <c r="E38">
-        <v>278.1</v>
+        <v>232.2</v>
       </c>
       <c r="F38">
         <v>263.4</v>
       </c>
       <c r="G38">
-        <v>256.5</v>
+        <v>244.8</v>
       </c>
       <c r="H38">
-        <v>232.2</v>
+        <v>262.5</v>
       </c>
       <c r="I38">
         <v>255.6</v>
       </c>
       <c r="J38">
-        <v>240</v>
+        <v>278.1</v>
       </c>
       <c r="K38">
-        <v>262.5</v>
+        <v>255.6</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -1741,34 +1741,34 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>240.9</v>
+        <v>236.1</v>
       </c>
       <c r="C39">
         <v>285.9</v>
       </c>
       <c r="D39">
-        <v>251.6999973006</v>
+        <v>252.6</v>
       </c>
       <c r="E39">
-        <v>274.2</v>
+        <v>228.3</v>
       </c>
       <c r="F39">
         <v>259.5</v>
       </c>
       <c r="G39">
-        <v>252.6</v>
+        <v>240.9</v>
       </c>
       <c r="H39">
-        <v>228.3</v>
+        <v>258.6</v>
       </c>
       <c r="I39">
         <v>251.7</v>
       </c>
       <c r="J39">
-        <v>236.1</v>
+        <v>274.2</v>
       </c>
       <c r="K39">
-        <v>258.6</v>
+        <v>251.7</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1776,34 +1776,34 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>237</v>
+        <v>232.2</v>
       </c>
       <c r="C40">
         <v>282</v>
       </c>
       <c r="D40">
-        <v>247.7999973006</v>
+        <v>248.7</v>
       </c>
       <c r="E40">
-        <v>270.3</v>
+        <v>224.4</v>
       </c>
       <c r="F40">
         <v>255.6</v>
       </c>
       <c r="G40">
-        <v>248.7</v>
+        <v>237</v>
       </c>
       <c r="H40">
-        <v>224.4</v>
+        <v>254.7</v>
       </c>
       <c r="I40">
         <v>247.8</v>
       </c>
       <c r="J40">
-        <v>232.2</v>
+        <v>270.3</v>
       </c>
       <c r="K40">
-        <v>254.7</v>
+        <v>247.8</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -1811,34 +1811,34 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>233.1</v>
+        <v>228.3</v>
       </c>
       <c r="C41">
         <v>278.1</v>
       </c>
       <c r="D41">
-        <v>243.8999973005</v>
+        <v>244.8</v>
       </c>
       <c r="E41">
-        <v>266.4</v>
+        <v>220.5</v>
       </c>
       <c r="F41">
         <v>251.7</v>
       </c>
       <c r="G41">
-        <v>244.8</v>
+        <v>233.1</v>
       </c>
       <c r="H41">
-        <v>220.5</v>
+        <v>250.8</v>
       </c>
       <c r="I41">
         <v>243.9</v>
       </c>
       <c r="J41">
-        <v>228.3</v>
+        <v>266.4</v>
       </c>
       <c r="K41">
-        <v>250.8</v>
+        <v>243.9</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -1846,34 +1846,34 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>229.2</v>
+        <v>224.4</v>
       </c>
       <c r="C42">
         <v>274.2</v>
       </c>
       <c r="D42">
-        <v>239.999997300375</v>
+        <v>240.9</v>
       </c>
       <c r="E42">
-        <v>262.5</v>
+        <v>216.6</v>
       </c>
       <c r="F42">
         <v>247.8</v>
       </c>
       <c r="G42">
-        <v>240.9</v>
+        <v>229.2</v>
       </c>
       <c r="H42">
-        <v>216.6</v>
+        <v>246.9</v>
       </c>
       <c r="I42">
         <v>240</v>
       </c>
       <c r="J42">
-        <v>224.4</v>
+        <v>262.5</v>
       </c>
       <c r="K42">
-        <v>246.9</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -1881,34 +1881,34 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>225.3</v>
+        <v>220.5</v>
       </c>
       <c r="C43">
         <v>270.3</v>
       </c>
       <c r="D43">
-        <v>236.0999973005</v>
+        <v>237</v>
       </c>
       <c r="E43">
-        <v>258.6</v>
+        <v>212.7</v>
       </c>
       <c r="F43">
         <v>243.9</v>
       </c>
       <c r="G43">
-        <v>237</v>
+        <v>225.3</v>
       </c>
       <c r="H43">
-        <v>212.7</v>
+        <v>243</v>
       </c>
       <c r="I43">
         <v>236.1</v>
       </c>
       <c r="J43">
-        <v>220.5</v>
+        <v>258.6</v>
       </c>
       <c r="K43">
-        <v>243</v>
+        <v>236.1</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -1916,34 +1916,34 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>221.4</v>
+        <v>216.6</v>
       </c>
       <c r="C44">
         <v>266.4</v>
       </c>
       <c r="D44">
-        <v>232.1999973004285</v>
+        <v>233.1</v>
       </c>
       <c r="E44">
-        <v>254.7</v>
+        <v>208.8</v>
       </c>
       <c r="F44">
         <v>240</v>
       </c>
       <c r="G44">
-        <v>233.1</v>
+        <v>221.4</v>
       </c>
       <c r="H44">
-        <v>208.8</v>
+        <v>239.1</v>
       </c>
       <c r="I44">
         <v>232.2</v>
       </c>
       <c r="J44">
-        <v>216.6</v>
+        <v>254.7</v>
       </c>
       <c r="K44">
-        <v>239.1</v>
+        <v>232.2</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -1951,34 +1951,34 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>217.5</v>
+        <v>212.7</v>
       </c>
       <c r="C45">
         <v>262.5</v>
       </c>
       <c r="D45">
-        <v>228.2999973005</v>
+        <v>229.2</v>
       </c>
       <c r="E45">
-        <v>250.8</v>
+        <v>204.9</v>
       </c>
       <c r="F45">
         <v>236.1</v>
       </c>
       <c r="G45">
-        <v>229.2</v>
+        <v>217.5</v>
       </c>
       <c r="H45">
-        <v>204.9</v>
+        <v>235.2</v>
       </c>
       <c r="I45">
         <v>228.3</v>
       </c>
       <c r="J45">
-        <v>212.7</v>
+        <v>250.8</v>
       </c>
       <c r="K45">
-        <v>235.2</v>
+        <v>228.3</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -1986,34 +1986,34 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>213.6</v>
+        <v>208.8</v>
       </c>
       <c r="C46">
         <v>258.6</v>
       </c>
       <c r="D46">
-        <v>224.3999973005</v>
+        <v>225.3</v>
       </c>
       <c r="E46">
-        <v>246.9</v>
+        <v>201</v>
       </c>
       <c r="F46">
         <v>232.2</v>
       </c>
       <c r="G46">
-        <v>225.3</v>
+        <v>213.6</v>
       </c>
       <c r="H46">
-        <v>201</v>
+        <v>231.3</v>
       </c>
       <c r="I46">
         <v>224.4</v>
       </c>
       <c r="J46">
-        <v>208.8</v>
+        <v>246.9</v>
       </c>
       <c r="K46">
-        <v>231.3</v>
+        <v>224.4</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2021,34 +2021,34 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>209.7</v>
+        <v>204.9</v>
       </c>
       <c r="C47">
         <v>254.7</v>
       </c>
       <c r="D47">
-        <v>220.4999973006</v>
+        <v>221.4</v>
       </c>
       <c r="E47">
-        <v>243</v>
+        <v>197.1</v>
       </c>
       <c r="F47">
         <v>228.3</v>
       </c>
       <c r="G47">
-        <v>221.4</v>
+        <v>209.7</v>
       </c>
       <c r="H47">
-        <v>197.1</v>
+        <v>227.4</v>
       </c>
       <c r="I47">
         <v>220.5</v>
       </c>
       <c r="J47">
-        <v>204.9</v>
+        <v>243</v>
       </c>
       <c r="K47">
-        <v>227.4</v>
+        <v>220.5</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2056,34 +2056,34 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>205.8</v>
+        <v>201</v>
       </c>
       <c r="C48">
         <v>250.8</v>
       </c>
       <c r="D48">
-        <v>216.5999973006</v>
+        <v>217.5</v>
       </c>
       <c r="E48">
-        <v>239.1</v>
+        <v>193.2</v>
       </c>
       <c r="F48">
         <v>224.4</v>
       </c>
       <c r="G48">
-        <v>217.5</v>
+        <v>205.8</v>
       </c>
       <c r="H48">
-        <v>193.2</v>
+        <v>223.5</v>
       </c>
       <c r="I48">
         <v>216.6</v>
       </c>
       <c r="J48">
-        <v>201</v>
+        <v>239.1</v>
       </c>
       <c r="K48">
-        <v>223.5</v>
+        <v>216.6</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2091,34 +2091,34 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>201.9</v>
+        <v>197.1</v>
       </c>
       <c r="C49">
         <v>246.9</v>
       </c>
       <c r="D49">
-        <v>212.6999973005</v>
+        <v>213.6</v>
       </c>
       <c r="E49">
-        <v>235.2</v>
+        <v>189.3</v>
       </c>
       <c r="F49">
         <v>220.5</v>
       </c>
       <c r="G49">
-        <v>213.6</v>
+        <v>201.9</v>
       </c>
       <c r="H49">
-        <v>189.3</v>
+        <v>219.6</v>
       </c>
       <c r="I49">
         <v>212.7</v>
       </c>
       <c r="J49">
-        <v>197.1</v>
+        <v>235.2</v>
       </c>
       <c r="K49">
-        <v>219.6</v>
+        <v>212.7</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2126,34 +2126,34 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>198</v>
+        <v>193.2</v>
       </c>
       <c r="C50">
         <v>243</v>
       </c>
       <c r="D50">
-        <v>208.7999973004285</v>
+        <v>209.7</v>
       </c>
       <c r="E50">
-        <v>231.3</v>
+        <v>185.4</v>
       </c>
       <c r="F50">
         <v>216.6</v>
       </c>
       <c r="G50">
-        <v>209.7</v>
+        <v>198</v>
       </c>
       <c r="H50">
-        <v>185.4</v>
+        <v>215.7</v>
       </c>
       <c r="I50">
         <v>208.8</v>
       </c>
       <c r="J50">
-        <v>193.2</v>
+        <v>231.3</v>
       </c>
       <c r="K50">
-        <v>215.7</v>
+        <v>208.8</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2161,34 +2161,34 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>194.1</v>
+        <v>189.3</v>
       </c>
       <c r="C51">
         <v>239.1</v>
       </c>
       <c r="D51">
-        <v>204.8999973004286</v>
+        <v>205.8</v>
       </c>
       <c r="E51">
-        <v>227.4</v>
+        <v>181.5</v>
       </c>
       <c r="F51">
         <v>212.7</v>
       </c>
       <c r="G51">
-        <v>205.8</v>
+        <v>194.1</v>
       </c>
       <c r="H51">
-        <v>181.5</v>
+        <v>211.8</v>
       </c>
       <c r="I51">
         <v>204.9</v>
       </c>
       <c r="J51">
-        <v>189.3</v>
+        <v>227.4</v>
       </c>
       <c r="K51">
-        <v>211.8</v>
+        <v>204.9</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2196,34 +2196,34 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>190.2</v>
+        <v>185.4</v>
       </c>
       <c r="C52">
         <v>235.2</v>
       </c>
       <c r="D52">
-        <v>200.999997300375</v>
+        <v>201.9</v>
       </c>
       <c r="E52">
-        <v>223.5</v>
+        <v>177.6</v>
       </c>
       <c r="F52">
         <v>208.8</v>
       </c>
       <c r="G52">
-        <v>201.9</v>
+        <v>190.2</v>
       </c>
       <c r="H52">
-        <v>177.6</v>
+        <v>207.9</v>
       </c>
       <c r="I52">
         <v>201</v>
       </c>
       <c r="J52">
-        <v>185.4</v>
+        <v>223.5</v>
       </c>
       <c r="K52">
-        <v>207.9</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2231,34 +2231,34 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>186.3</v>
+        <v>181.5</v>
       </c>
       <c r="C53">
         <v>231.3</v>
       </c>
       <c r="D53">
-        <v>197.0999973003333</v>
+        <v>198</v>
       </c>
       <c r="E53">
-        <v>219.6</v>
+        <v>173.7</v>
       </c>
       <c r="F53">
         <v>204.9</v>
       </c>
       <c r="G53">
-        <v>198</v>
+        <v>186.3</v>
       </c>
       <c r="H53">
-        <v>173.7</v>
+        <v>204</v>
       </c>
       <c r="I53">
         <v>197.1</v>
       </c>
       <c r="J53">
-        <v>181.5</v>
+        <v>219.6</v>
       </c>
       <c r="K53">
-        <v>204</v>
+        <v>197.1</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2266,34 +2266,34 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>182.4</v>
+        <v>177.6</v>
       </c>
       <c r="C54">
         <v>227.4</v>
       </c>
       <c r="D54">
-        <v>193.1999973004286</v>
+        <v>194.1</v>
       </c>
       <c r="E54">
-        <v>215.7</v>
+        <v>169.8</v>
       </c>
       <c r="F54">
         <v>201</v>
       </c>
       <c r="G54">
-        <v>194.1</v>
+        <v>182.4</v>
       </c>
       <c r="H54">
-        <v>169.8</v>
+        <v>200.1</v>
       </c>
       <c r="I54">
         <v>193.2</v>
       </c>
       <c r="J54">
-        <v>177.6</v>
+        <v>215.7</v>
       </c>
       <c r="K54">
-        <v>200.1</v>
+        <v>193.2</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2301,34 +2301,34 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>178.5</v>
+        <v>173.7</v>
       </c>
       <c r="C55">
         <v>223.5</v>
       </c>
       <c r="D55">
-        <v>189.2999973004285</v>
+        <v>190.2</v>
       </c>
       <c r="E55">
-        <v>211.8</v>
+        <v>165.9</v>
       </c>
       <c r="F55">
         <v>197.1</v>
       </c>
       <c r="G55">
-        <v>190.2</v>
+        <v>178.5</v>
       </c>
       <c r="H55">
-        <v>165.9</v>
+        <v>196.2</v>
       </c>
       <c r="I55">
         <v>189.3</v>
       </c>
       <c r="J55">
-        <v>173.7</v>
+        <v>211.8</v>
       </c>
       <c r="K55">
-        <v>196.2</v>
+        <v>189.3</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2336,34 +2336,34 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>174.6</v>
+        <v>169.8</v>
       </c>
       <c r="C56">
         <v>219.6</v>
       </c>
       <c r="D56">
-        <v>185.3999973003333</v>
+        <v>186.3</v>
       </c>
       <c r="E56">
-        <v>207.9</v>
+        <v>162</v>
       </c>
       <c r="F56">
         <v>193.2</v>
       </c>
       <c r="G56">
-        <v>186.3</v>
+        <v>174.6</v>
       </c>
       <c r="H56">
-        <v>162</v>
+        <v>192.3</v>
       </c>
       <c r="I56">
         <v>185.4</v>
       </c>
       <c r="J56">
-        <v>169.8</v>
+        <v>207.9</v>
       </c>
       <c r="K56">
-        <v>192.3</v>
+        <v>185.4</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2371,34 +2371,34 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>170.7</v>
+        <v>165.9</v>
       </c>
       <c r="C57">
         <v>215.7</v>
       </c>
       <c r="D57">
-        <v>181.4999973006</v>
+        <v>182.4</v>
       </c>
       <c r="E57">
-        <v>204</v>
+        <v>158.1</v>
       </c>
       <c r="F57">
         <v>189.3</v>
       </c>
       <c r="G57">
-        <v>182.4</v>
+        <v>170.7</v>
       </c>
       <c r="H57">
-        <v>158.1</v>
+        <v>188.4</v>
       </c>
       <c r="I57">
         <v>181.5</v>
       </c>
       <c r="J57">
-        <v>165.9</v>
+        <v>204</v>
       </c>
       <c r="K57">
-        <v>188.4</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2406,34 +2406,34 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>166.8</v>
+        <v>162</v>
       </c>
       <c r="C58">
         <v>211.8</v>
       </c>
       <c r="D58">
-        <v>177.5999973004286</v>
+        <v>178.5</v>
       </c>
       <c r="E58">
-        <v>200.1</v>
+        <v>154.2</v>
       </c>
       <c r="F58">
         <v>185.4</v>
       </c>
       <c r="G58">
-        <v>178.5</v>
+        <v>166.8</v>
       </c>
       <c r="H58">
-        <v>154.2</v>
+        <v>184.5</v>
       </c>
       <c r="I58">
         <v>177.6</v>
       </c>
       <c r="J58">
-        <v>162</v>
+        <v>200.1</v>
       </c>
       <c r="K58">
-        <v>184.5</v>
+        <v>177.6</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2441,34 +2441,34 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>162.9</v>
+        <v>158.1</v>
       </c>
       <c r="C59">
         <v>207.9</v>
       </c>
       <c r="D59">
-        <v>173.6999973005</v>
+        <v>174.6</v>
       </c>
       <c r="E59">
-        <v>196.2</v>
+        <v>150.3</v>
       </c>
       <c r="F59">
         <v>181.5</v>
       </c>
       <c r="G59">
-        <v>174.6</v>
+        <v>162.9</v>
       </c>
       <c r="H59">
-        <v>150.3</v>
+        <v>180.6</v>
       </c>
       <c r="I59">
         <v>173.7</v>
       </c>
       <c r="J59">
-        <v>158.1</v>
+        <v>196.2</v>
       </c>
       <c r="K59">
-        <v>180.6</v>
+        <v>173.7</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -2476,34 +2476,34 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>159</v>
+        <v>154.2</v>
       </c>
       <c r="C60">
         <v>204</v>
       </c>
       <c r="D60">
-        <v>169.7999973004285</v>
+        <v>170.7</v>
       </c>
       <c r="E60">
-        <v>192.3</v>
+        <v>146.4</v>
       </c>
       <c r="F60">
         <v>177.6</v>
       </c>
       <c r="G60">
-        <v>170.7</v>
+        <v>159</v>
       </c>
       <c r="H60">
-        <v>146.4</v>
+        <v>176.7</v>
       </c>
       <c r="I60">
         <v>169.8</v>
       </c>
       <c r="J60">
-        <v>154.2</v>
+        <v>192.3</v>
       </c>
       <c r="K60">
-        <v>176.7</v>
+        <v>169.8</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2511,34 +2511,34 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>155.1</v>
+        <v>150.3</v>
       </c>
       <c r="C61">
         <v>200.1</v>
       </c>
       <c r="D61">
-        <v>165.8999973005999</v>
+        <v>166.8</v>
       </c>
       <c r="E61">
-        <v>188.4</v>
+        <v>142.5</v>
       </c>
       <c r="F61">
         <v>173.7</v>
       </c>
       <c r="G61">
-        <v>166.8</v>
+        <v>155.1</v>
       </c>
       <c r="H61">
-        <v>142.5</v>
+        <v>172.8</v>
       </c>
       <c r="I61">
         <v>165.9</v>
       </c>
       <c r="J61">
-        <v>150.3</v>
+        <v>188.4</v>
       </c>
       <c r="K61">
-        <v>172.8</v>
+        <v>165.9</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -2546,34 +2546,34 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>151.2</v>
+        <v>146.4</v>
       </c>
       <c r="C62">
         <v>196.2</v>
       </c>
       <c r="D62">
-        <v>161.9999973006</v>
+        <v>162.9</v>
       </c>
       <c r="E62">
-        <v>184.5</v>
+        <v>138.6</v>
       </c>
       <c r="F62">
         <v>169.8</v>
       </c>
       <c r="G62">
-        <v>162.9</v>
+        <v>151.2</v>
       </c>
       <c r="H62">
-        <v>138.6</v>
+        <v>168.9</v>
       </c>
       <c r="I62">
         <v>162</v>
       </c>
       <c r="J62">
-        <v>146.4</v>
+        <v>184.5</v>
       </c>
       <c r="K62">
-        <v>168.9</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -2581,34 +2581,34 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>147.3</v>
+        <v>142.5</v>
       </c>
       <c r="C63">
         <v>192.3</v>
       </c>
       <c r="D63">
-        <v>158.099997300375</v>
+        <v>159</v>
       </c>
       <c r="E63">
-        <v>180.6</v>
+        <v>134.7</v>
       </c>
       <c r="F63">
         <v>165.9</v>
       </c>
       <c r="G63">
-        <v>159</v>
+        <v>147.3</v>
       </c>
       <c r="H63">
-        <v>134.7</v>
+        <v>165</v>
       </c>
       <c r="I63">
         <v>158.1</v>
       </c>
       <c r="J63">
-        <v>142.5</v>
+        <v>180.6</v>
       </c>
       <c r="K63">
-        <v>165</v>
+        <v>158.1</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -2616,34 +2616,34 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>143.4</v>
+        <v>138.6</v>
       </c>
       <c r="C64">
         <v>188.4</v>
       </c>
       <c r="D64">
-        <v>154.199997300375</v>
+        <v>155.1</v>
       </c>
       <c r="E64">
-        <v>176.7</v>
+        <v>130.8</v>
       </c>
       <c r="F64">
         <v>162</v>
       </c>
       <c r="G64">
-        <v>155.1</v>
+        <v>143.4</v>
       </c>
       <c r="H64">
-        <v>130.8</v>
+        <v>161.1</v>
       </c>
       <c r="I64">
         <v>154.2</v>
       </c>
       <c r="J64">
-        <v>138.6</v>
+        <v>176.7</v>
       </c>
       <c r="K64">
-        <v>161.1</v>
+        <v>154.2</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -2651,34 +2651,34 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>139.5</v>
+        <v>134.7</v>
       </c>
       <c r="C65">
         <v>184.5</v>
       </c>
       <c r="D65">
-        <v>150.2999973006</v>
+        <v>151.2</v>
       </c>
       <c r="E65">
-        <v>172.8</v>
+        <v>126.9</v>
       </c>
       <c r="F65">
         <v>158.1</v>
       </c>
       <c r="G65">
-        <v>151.2</v>
+        <v>139.5</v>
       </c>
       <c r="H65">
-        <v>126.9</v>
+        <v>157.2</v>
       </c>
       <c r="I65">
         <v>150.3</v>
       </c>
       <c r="J65">
-        <v>134.7</v>
+        <v>172.8</v>
       </c>
       <c r="K65">
-        <v>157.2</v>
+        <v>150.3</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -2686,34 +2686,34 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>135.6</v>
+        <v>130.8</v>
       </c>
       <c r="C66">
         <v>180.6</v>
       </c>
       <c r="D66">
-        <v>146.3999973006</v>
+        <v>147.3</v>
       </c>
       <c r="E66">
-        <v>168.9</v>
+        <v>123</v>
       </c>
       <c r="F66">
         <v>154.2</v>
       </c>
       <c r="G66">
-        <v>147.3</v>
+        <v>135.6</v>
       </c>
       <c r="H66">
-        <v>123</v>
+        <v>153.3</v>
       </c>
       <c r="I66">
         <v>146.4</v>
       </c>
       <c r="J66">
-        <v>130.8</v>
+        <v>168.9</v>
       </c>
       <c r="K66">
-        <v>153.3</v>
+        <v>146.4</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -2721,34 +2721,34 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>131.7</v>
+        <v>126.9</v>
       </c>
       <c r="C67">
         <v>176.7</v>
       </c>
       <c r="D67">
-        <v>142.4999973006</v>
+        <v>143.4</v>
       </c>
       <c r="E67">
-        <v>165</v>
+        <v>119.1</v>
       </c>
       <c r="F67">
         <v>150.3</v>
       </c>
       <c r="G67">
-        <v>143.4</v>
+        <v>131.7</v>
       </c>
       <c r="H67">
-        <v>119.1</v>
+        <v>149.4</v>
       </c>
       <c r="I67">
         <v>142.5</v>
       </c>
       <c r="J67">
-        <v>126.9</v>
+        <v>165</v>
       </c>
       <c r="K67">
-        <v>149.4</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -2756,34 +2756,34 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>127.8</v>
+        <v>123</v>
       </c>
       <c r="C68">
         <v>172.8</v>
       </c>
       <c r="D68">
-        <v>138.5999973006</v>
+        <v>139.5</v>
       </c>
       <c r="E68">
-        <v>161.1</v>
+        <v>115.2</v>
       </c>
       <c r="F68">
         <v>146.4</v>
       </c>
       <c r="G68">
-        <v>139.5</v>
+        <v>127.8</v>
       </c>
       <c r="H68">
-        <v>115.2</v>
+        <v>145.5</v>
       </c>
       <c r="I68">
         <v>138.6</v>
       </c>
       <c r="J68">
-        <v>123</v>
+        <v>161.1</v>
       </c>
       <c r="K68">
-        <v>145.5</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -2791,34 +2791,34 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>123.9</v>
+        <v>119.1</v>
       </c>
       <c r="C69">
         <v>168.9</v>
       </c>
       <c r="D69">
-        <v>134.6999973005</v>
+        <v>135.6</v>
       </c>
       <c r="E69">
-        <v>157.2</v>
+        <v>111.3</v>
       </c>
       <c r="F69">
         <v>142.5</v>
       </c>
       <c r="G69">
-        <v>135.6</v>
+        <v>123.9</v>
       </c>
       <c r="H69">
-        <v>111.3</v>
+        <v>141.6</v>
       </c>
       <c r="I69">
         <v>134.7</v>
       </c>
       <c r="J69">
-        <v>119.1</v>
+        <v>157.2</v>
       </c>
       <c r="K69">
-        <v>141.6</v>
+        <v>134.7</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -2826,34 +2826,34 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>120</v>
+        <v>115.2</v>
       </c>
       <c r="C70">
         <v>165</v>
       </c>
       <c r="D70">
-        <v>130.7999973005</v>
+        <v>131.7</v>
       </c>
       <c r="E70">
-        <v>153.3</v>
+        <v>107.4</v>
       </c>
       <c r="F70">
         <v>138.6</v>
       </c>
       <c r="G70">
-        <v>131.7</v>
+        <v>120</v>
       </c>
       <c r="H70">
-        <v>107.4</v>
+        <v>137.7</v>
       </c>
       <c r="I70">
         <v>130.8</v>
       </c>
       <c r="J70">
-        <v>115.2</v>
+        <v>153.3</v>
       </c>
       <c r="K70">
-        <v>137.7</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -2861,34 +2861,34 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>116.1</v>
+        <v>111.3</v>
       </c>
       <c r="C71">
         <v>161.1</v>
       </c>
       <c r="D71">
-        <v>126.8999973006</v>
+        <v>127.8</v>
       </c>
       <c r="E71">
-        <v>149.4</v>
+        <v>103.5</v>
       </c>
       <c r="F71">
         <v>134.7</v>
       </c>
       <c r="G71">
-        <v>127.8</v>
+        <v>116.1</v>
       </c>
       <c r="H71">
-        <v>103.5</v>
+        <v>133.8</v>
       </c>
       <c r="I71">
         <v>126.9</v>
       </c>
       <c r="J71">
-        <v>111.3</v>
+        <v>149.4</v>
       </c>
       <c r="K71">
-        <v>133.8</v>
+        <v>126.9</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -2896,34 +2896,34 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>112.2</v>
+        <v>107.4</v>
       </c>
       <c r="C72">
         <v>157.2</v>
       </c>
       <c r="D72">
-        <v>122.9999973005</v>
+        <v>123.9</v>
       </c>
       <c r="E72">
-        <v>145.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F72">
         <v>130.8</v>
       </c>
       <c r="G72">
-        <v>123.9</v>
+        <v>112.2</v>
       </c>
       <c r="H72">
-        <v>99.59999999999999</v>
+        <v>129.9</v>
       </c>
       <c r="I72">
         <v>123</v>
       </c>
       <c r="J72">
-        <v>107.4</v>
+        <v>145.5</v>
       </c>
       <c r="K72">
-        <v>129.9</v>
+        <v>123</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -2931,34 +2931,34 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>108.3</v>
+        <v>103.5</v>
       </c>
       <c r="C73">
         <v>153.3</v>
       </c>
       <c r="D73">
-        <v>119.0999973006</v>
+        <v>120</v>
       </c>
       <c r="E73">
-        <v>141.6</v>
+        <v>95.7</v>
       </c>
       <c r="F73">
         <v>126.9</v>
       </c>
       <c r="G73">
-        <v>120</v>
+        <v>108.3</v>
       </c>
       <c r="H73">
-        <v>95.7</v>
+        <v>126</v>
       </c>
       <c r="I73">
         <v>119.1</v>
       </c>
       <c r="J73">
-        <v>103.5</v>
+        <v>141.6</v>
       </c>
       <c r="K73">
-        <v>126</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -2966,34 +2966,34 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>104.4</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C74">
         <v>149.4</v>
       </c>
       <c r="D74">
-        <v>115.1999973006</v>
+        <v>116.1</v>
       </c>
       <c r="E74">
-        <v>137.7</v>
+        <v>91.8</v>
       </c>
       <c r="F74">
         <v>123</v>
       </c>
       <c r="G74">
-        <v>116.1</v>
+        <v>104.4</v>
       </c>
       <c r="H74">
-        <v>91.8</v>
+        <v>122.1</v>
       </c>
       <c r="I74">
         <v>115.2</v>
       </c>
       <c r="J74">
-        <v>99.59999999999999</v>
+        <v>137.7</v>
       </c>
       <c r="K74">
-        <v>122.1</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -3001,34 +3001,34 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>100.5</v>
+        <v>95.7</v>
       </c>
       <c r="C75">
         <v>145.5</v>
       </c>
       <c r="D75">
-        <v>111.2999973006</v>
+        <v>112.2</v>
       </c>
       <c r="E75">
-        <v>133.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F75">
         <v>119.1</v>
       </c>
       <c r="G75">
-        <v>112.2</v>
+        <v>100.5</v>
       </c>
       <c r="H75">
-        <v>87.89999999999999</v>
+        <v>118.2</v>
       </c>
       <c r="I75">
         <v>111.3</v>
       </c>
       <c r="J75">
-        <v>95.7</v>
+        <v>133.8</v>
       </c>
       <c r="K75">
-        <v>118.2</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3036,34 +3036,34 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>96.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C76">
         <v>141.6</v>
       </c>
       <c r="D76">
-        <v>107.3999973006</v>
+        <v>108.3</v>
       </c>
       <c r="E76">
-        <v>129.9</v>
+        <v>84</v>
       </c>
       <c r="F76">
         <v>115.2</v>
       </c>
       <c r="G76">
-        <v>108.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H76">
-        <v>84</v>
+        <v>114.3</v>
       </c>
       <c r="I76">
         <v>107.4</v>
       </c>
       <c r="J76">
-        <v>91.8</v>
+        <v>129.9</v>
       </c>
       <c r="K76">
-        <v>114.3</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -3071,34 +3071,34 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>92.7</v>
+        <v>91.8</v>
       </c>
       <c r="C77">
         <v>137.7</v>
       </c>
       <c r="D77">
-        <v>103.4999973006</v>
+        <v>104.4</v>
       </c>
       <c r="E77">
-        <v>126</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F77">
         <v>111.3</v>
       </c>
       <c r="G77">
-        <v>104.4</v>
+        <v>92.7</v>
       </c>
       <c r="H77">
-        <v>80.09999999999999</v>
+        <v>110.4</v>
       </c>
       <c r="I77">
         <v>103.5</v>
       </c>
       <c r="J77">
-        <v>91.8</v>
+        <v>126</v>
       </c>
       <c r="K77">
-        <v>110.4</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -3106,34 +3106,34 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>88.8</v>
+        <v>91.8</v>
       </c>
       <c r="C78">
         <v>133.8</v>
       </c>
       <c r="D78">
-        <v>99.59999730059999</v>
+        <v>100.5</v>
       </c>
       <c r="E78">
-        <v>122.1</v>
+        <v>76.2</v>
       </c>
       <c r="F78">
         <v>107.4</v>
       </c>
       <c r="G78">
-        <v>100.5</v>
+        <v>88.8</v>
       </c>
       <c r="H78">
-        <v>76.2</v>
+        <v>106.5</v>
       </c>
       <c r="I78">
         <v>99.59999999999999</v>
       </c>
       <c r="J78">
-        <v>91.8</v>
+        <v>122.1</v>
       </c>
       <c r="K78">
-        <v>106.5</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3141,34 +3141,34 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C79">
         <v>129.9</v>
       </c>
       <c r="D79">
-        <v>95.6999973006</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E79">
-        <v>118.2</v>
+        <v>72.3</v>
       </c>
       <c r="F79">
         <v>103.5</v>
       </c>
       <c r="G79">
-        <v>96.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H79">
-        <v>72.3</v>
+        <v>102.6</v>
       </c>
       <c r="I79">
         <v>95.7</v>
       </c>
       <c r="J79">
-        <v>91.8</v>
+        <v>118.2</v>
       </c>
       <c r="K79">
-        <v>102.6</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -3176,34 +3176,34 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C80">
         <v>126</v>
       </c>
       <c r="D80">
-        <v>91.7999973006</v>
+        <v>92.7</v>
       </c>
       <c r="E80">
-        <v>114.3</v>
+        <v>72.3</v>
       </c>
       <c r="F80">
         <v>99.59999999999999</v>
       </c>
       <c r="G80">
-        <v>92.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H80">
-        <v>72.3</v>
+        <v>98.7</v>
       </c>
       <c r="I80">
         <v>91.8</v>
       </c>
       <c r="J80">
+        <v>114.3</v>
+      </c>
+      <c r="K80">
         <v>91.8</v>
-      </c>
-      <c r="K80">
-        <v>98.7</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3211,34 +3211,34 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C81">
         <v>122.1</v>
       </c>
       <c r="D81">
-        <v>87.89999730059999</v>
+        <v>88.8</v>
       </c>
       <c r="E81">
-        <v>110.4</v>
+        <v>72.3</v>
       </c>
       <c r="F81">
         <v>95.7</v>
       </c>
       <c r="G81">
-        <v>88.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H81">
-        <v>72.3</v>
+        <v>94.8</v>
       </c>
       <c r="I81">
-        <v>87.89999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="J81">
-        <v>91.8</v>
+        <v>110.4</v>
       </c>
       <c r="K81">
-        <v>94.8</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3246,34 +3246,34 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C82">
         <v>118.2</v>
       </c>
       <c r="D82">
-        <v>83.9999973006</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E82">
-        <v>106.5</v>
+        <v>72.3</v>
       </c>
       <c r="F82">
         <v>91.8</v>
       </c>
       <c r="G82">
-        <v>84.89999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H82">
-        <v>72.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I82">
         <v>84</v>
       </c>
       <c r="J82">
-        <v>91.8</v>
+        <v>106.5</v>
       </c>
       <c r="K82">
-        <v>90.89999999999999</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3281,34 +3281,34 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C83">
         <v>114.3</v>
       </c>
       <c r="D83">
-        <v>80.09999730059999</v>
+        <v>81</v>
       </c>
       <c r="E83">
-        <v>102.6</v>
+        <v>72.3</v>
       </c>
       <c r="F83">
-        <v>87.89999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G83">
-        <v>81</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H83">
-        <v>72.3</v>
+        <v>87</v>
       </c>
       <c r="I83">
         <v>80.09999999999999</v>
       </c>
       <c r="J83">
-        <v>91.8</v>
+        <v>102.6</v>
       </c>
       <c r="K83">
-        <v>87</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3316,34 +3316,34 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C84">
         <v>110.4</v>
       </c>
       <c r="D84">
-        <v>76.19999730075</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E84">
-        <v>98.7</v>
+        <v>72.3</v>
       </c>
       <c r="F84">
         <v>84</v>
       </c>
       <c r="G84">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H84">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I84">
         <v>76.2</v>
       </c>
       <c r="J84">
-        <v>91.8</v>
+        <v>98.7</v>
       </c>
       <c r="K84">
-        <v>83.09999999999999</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3351,34 +3351,34 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C85">
         <v>106.5</v>
       </c>
       <c r="D85">
-        <v>72.2999973015</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E85">
-        <v>94.8</v>
+        <v>72.3</v>
       </c>
       <c r="F85">
         <v>80.09999999999999</v>
       </c>
       <c r="G85">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H85">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I85">
         <v>72.3</v>
       </c>
       <c r="J85">
-        <v>91.8</v>
+        <v>94.8</v>
       </c>
       <c r="K85">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -3386,34 +3386,34 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C86">
         <v>102.6</v>
       </c>
       <c r="D86">
-        <v>72.2999973015</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E86">
-        <v>90.89999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F86">
         <v>80.09999999999999</v>
       </c>
       <c r="G86">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H86">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I86">
         <v>72.3</v>
       </c>
       <c r="J86">
-        <v>91.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K86">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -3421,34 +3421,34 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C87">
         <v>98.7</v>
       </c>
       <c r="D87">
-        <v>72.2999973015</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E87">
-        <v>87</v>
+        <v>72.3</v>
       </c>
       <c r="F87">
         <v>80.09999999999999</v>
       </c>
       <c r="G87">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H87">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I87">
         <v>72.3</v>
       </c>
       <c r="J87">
-        <v>91.8</v>
+        <v>87</v>
       </c>
       <c r="K87">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -3456,34 +3456,34 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C88">
         <v>94.8</v>
       </c>
       <c r="D88">
-        <v>72.2999973015</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E88">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F88">
         <v>80.09999999999999</v>
       </c>
       <c r="G88">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H88">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I88">
         <v>72.3</v>
       </c>
       <c r="J88">
-        <v>91.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K88">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -3491,34 +3491,34 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C89">
-        <v>90.89999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D89">
-        <v>72.2999973015</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E89">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F89">
         <v>80.09999999999999</v>
       </c>
       <c r="G89">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H89">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I89">
         <v>72.3</v>
       </c>
       <c r="J89">
-        <v>91.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K89">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3526,34 +3526,34 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C90">
         <v>87</v>
       </c>
       <c r="D90">
-        <v>72.2999973015</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E90">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F90">
         <v>80.09999999999999</v>
       </c>
       <c r="G90">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H90">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I90">
         <v>72.3</v>
       </c>
       <c r="J90">
-        <v>91.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K90">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -3561,34 +3561,34 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C91">
         <v>83.09999999999999</v>
       </c>
       <c r="D91">
-        <v>72.29999730300001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E91">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F91">
         <v>80.09999999999999</v>
       </c>
       <c r="G91">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H91">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I91">
         <v>72.3</v>
       </c>
       <c r="J91">
-        <v>91.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K91">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -3596,34 +3596,34 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C92">
         <v>83.09999999999999</v>
       </c>
       <c r="D92">
-        <v>72.29999730300001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E92">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F92">
         <v>80.09999999999999</v>
       </c>
       <c r="G92">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H92">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I92">
         <v>72.3</v>
       </c>
       <c r="J92">
-        <v>91.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K92">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -3631,34 +3631,34 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C93">
         <v>83.09999999999999</v>
       </c>
       <c r="D93">
-        <v>72.29999730300001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E93">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F93">
         <v>80.09999999999999</v>
       </c>
       <c r="G93">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H93">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I93">
         <v>72.3</v>
       </c>
       <c r="J93">
-        <v>91.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K93">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -3666,34 +3666,34 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C94">
         <v>83.09999999999999</v>
       </c>
       <c r="D94">
-        <v>72.29999730300001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E94">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F94">
         <v>80.09999999999999</v>
       </c>
       <c r="G94">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H94">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I94">
         <v>72.3</v>
       </c>
       <c r="J94">
-        <v>91.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K94">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -3701,34 +3701,34 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C95">
         <v>83.09999999999999</v>
       </c>
       <c r="D95">
-        <v>72.29999730300001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E95">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F95">
         <v>80.09999999999999</v>
       </c>
       <c r="G95">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H95">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I95">
         <v>72.3</v>
       </c>
       <c r="J95">
-        <v>91.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K95">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -3736,34 +3736,34 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C96">
         <v>83.09999999999999</v>
       </c>
       <c r="D96">
-        <v>72.29999730300001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E96">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F96">
         <v>80.09999999999999</v>
       </c>
       <c r="G96">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H96">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I96">
         <v>72.3</v>
       </c>
       <c r="J96">
-        <v>91.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K96">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -3771,34 +3771,34 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>84.89999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="C97">
         <v>83.09999999999999</v>
       </c>
       <c r="D97">
-        <v>72.29999730300001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E97">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F97">
         <v>80.09999999999999</v>
       </c>
       <c r="G97">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H97">
-        <v>72.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I97">
         <v>72.3</v>
       </c>
       <c r="J97">
-        <v>91.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K97">
-        <v>83.09999999999999</v>
+        <v>72.3</v>
       </c>
     </row>
   </sheetData>
@@ -4181,7 +4181,7 @@
         <v>20</v>
       </c>
       <c r="H11">
-        <v>26.46551724137931</v>
+        <v>20</v>
       </c>
       <c r="I11">
         <v>20</v>
@@ -4216,7 +4216,7 @@
         <v>20</v>
       </c>
       <c r="H12">
-        <v>26.46551724137931</v>
+        <v>20</v>
       </c>
       <c r="I12">
         <v>20</v>
@@ -4242,7 +4242,7 @@
         <v>20</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>26.46551724137931</v>
       </c>
       <c r="F13">
         <v>20</v>
@@ -4251,7 +4251,7 @@
         <v>20</v>
       </c>
       <c r="H13">
-        <v>26.46551724137931</v>
+        <v>20</v>
       </c>
       <c r="I13">
         <v>20</v>
@@ -4277,7 +4277,7 @@
         <v>26.46551724137931</v>
       </c>
       <c r="E14">
-        <v>26.46551724137931</v>
+        <v>32.93103448275862</v>
       </c>
       <c r="F14">
         <v>26.46551724137931</v>
@@ -4286,7 +4286,7 @@
         <v>26.46551724137931</v>
       </c>
       <c r="H14">
-        <v>32.93103448275862</v>
+        <v>26.46551724137931</v>
       </c>
       <c r="I14">
         <v>26.46551724137931</v>
@@ -4312,7 +4312,7 @@
         <v>32.93103448275862</v>
       </c>
       <c r="E15">
-        <v>32.93103448275862</v>
+        <v>39.39655172413793</v>
       </c>
       <c r="F15">
         <v>32.93103448275862</v>
@@ -4321,7 +4321,7 @@
         <v>32.93103448275862</v>
       </c>
       <c r="H15">
-        <v>39.39655172413793</v>
+        <v>32.93103448275862</v>
       </c>
       <c r="I15">
         <v>32.93103448275862</v>
@@ -4347,7 +4347,7 @@
         <v>39.39655172413793</v>
       </c>
       <c r="E16">
-        <v>39.39655172413793</v>
+        <v>45.86206896551724</v>
       </c>
       <c r="F16">
         <v>39.39655172413793</v>
@@ -4356,7 +4356,7 @@
         <v>39.39655172413793</v>
       </c>
       <c r="H16">
-        <v>45.86206896551724</v>
+        <v>39.39655172413793</v>
       </c>
       <c r="I16">
         <v>39.39655172413793</v>
@@ -4382,7 +4382,7 @@
         <v>45.86206896551724</v>
       </c>
       <c r="E17">
-        <v>45.86206896551724</v>
+        <v>52.32758620689656</v>
       </c>
       <c r="F17">
         <v>45.86206896551724</v>
@@ -4391,7 +4391,7 @@
         <v>45.86206896551724</v>
       </c>
       <c r="H17">
-        <v>52.32758620689656</v>
+        <v>45.86206896551724</v>
       </c>
       <c r="I17">
         <v>45.86206896551724</v>
@@ -4417,7 +4417,7 @@
         <v>52.32758620689656</v>
       </c>
       <c r="E18">
-        <v>52.32758620689656</v>
+        <v>58.79310344827586</v>
       </c>
       <c r="F18">
         <v>52.32758620689656</v>
@@ -4426,7 +4426,7 @@
         <v>52.32758620689656</v>
       </c>
       <c r="H18">
-        <v>58.79310344827586</v>
+        <v>52.32758620689656</v>
       </c>
       <c r="I18">
         <v>52.32758620689656</v>
@@ -4452,7 +4452,7 @@
         <v>58.79310344827586</v>
       </c>
       <c r="E19">
-        <v>58.79310344827586</v>
+        <v>65.25862068965517</v>
       </c>
       <c r="F19">
         <v>58.79310344827586</v>
@@ -4461,7 +4461,7 @@
         <v>58.79310344827586</v>
       </c>
       <c r="H19">
-        <v>65.25862068965517</v>
+        <v>58.79310344827586</v>
       </c>
       <c r="I19">
         <v>58.79310344827586</v>
@@ -4487,7 +4487,7 @@
         <v>65.25862068965517</v>
       </c>
       <c r="E20">
-        <v>65.25862068965517</v>
+        <v>71.72413793103448</v>
       </c>
       <c r="F20">
         <v>65.25862068965517</v>
@@ -4496,7 +4496,7 @@
         <v>65.25862068965517</v>
       </c>
       <c r="H20">
-        <v>71.72413793103448</v>
+        <v>65.25862068965517</v>
       </c>
       <c r="I20">
         <v>65.25862068965517</v>
@@ -4522,7 +4522,7 @@
         <v>71.72413793103448</v>
       </c>
       <c r="E21">
-        <v>71.72413793103448</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="F21">
         <v>71.72413793103448</v>
@@ -4531,7 +4531,7 @@
         <v>71.72413793103448</v>
       </c>
       <c r="H21">
-        <v>78.18965517241378</v>
+        <v>71.72413793103448</v>
       </c>
       <c r="I21">
         <v>71.72413793103448</v>
@@ -4548,34 +4548,34 @@
         <v>21</v>
       </c>
       <c r="B22">
+        <v>78.18965517241381</v>
+      </c>
+      <c r="C22">
+        <v>78.18965517241381</v>
+      </c>
+      <c r="D22">
         <v>71.72413793103448</v>
       </c>
-      <c r="C22">
-        <v>78.18965517241378</v>
-      </c>
-      <c r="D22">
-        <v>78.18965517241378</v>
-      </c>
       <c r="E22">
-        <v>78.18965517241378</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="F22">
-        <v>78.18965517241378</v>
+        <v>71.72413793103448</v>
       </c>
       <c r="G22">
-        <v>78.18965517241378</v>
+        <v>71.72413793103448</v>
       </c>
       <c r="H22">
-        <v>84.6551724137931</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="I22">
-        <v>78.18965517241378</v>
+        <v>71.72413793103448</v>
       </c>
       <c r="J22">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="K22">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4583,34 +4583,34 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>78.18965517241378</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="C23">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="D23">
-        <v>84.65517163836206</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E23">
-        <v>78.18965517241378</v>
+        <v>83.53448275862068</v>
       </c>
       <c r="F23">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="G23">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="H23">
-        <v>83.53448275862068</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="I23">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="J23">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="K23">
-        <v>84.6551724137931</v>
+        <v>78.18965517241381</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4618,34 +4618,34 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>78.18965517241378</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="C24">
-        <v>91.1206896551724</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="D24">
-        <v>84.65517163814654</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E24">
-        <v>84.6551724137931</v>
+        <v>82.41379310344827</v>
       </c>
       <c r="F24">
-        <v>84.6551724137931</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="G24">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="H24">
-        <v>82.41379310344827</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="I24">
-        <v>84.6551724137931</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="J24">
-        <v>84.6551724137931</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="K24">
-        <v>91.1206896551724</v>
+        <v>78.18965517241381</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4653,34 +4653,34 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>78.18965517241378</v>
+        <v>83.53448275862068</v>
       </c>
       <c r="C25">
-        <v>91.1206896551724</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="D25">
-        <v>84.65517163836206</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E25">
-        <v>91.1206896551724</v>
+        <v>81.29310344827586</v>
       </c>
       <c r="F25">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="G25">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="H25">
-        <v>81.29310344827586</v>
+        <v>90</v>
       </c>
       <c r="I25">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="J25">
-        <v>83.53448275862068</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="K25">
-        <v>90</v>
+        <v>84.65517241379311</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4688,34 +4688,34 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>78.18965517241378</v>
+        <v>82.41379310344827</v>
       </c>
       <c r="C26">
-        <v>91.1206896551724</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="D26">
-        <v>84.65517163836206</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E26">
-        <v>91.1206896551724</v>
+        <v>80.17241379310344</v>
       </c>
       <c r="F26">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="G26">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="H26">
-        <v>80.17241379310344</v>
+        <v>88.87931034482759</v>
       </c>
       <c r="I26">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="J26">
-        <v>82.41379310344827</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="K26">
-        <v>88.87931034482759</v>
+        <v>84.65517241379311</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4723,34 +4723,34 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>78.18965517241378</v>
+        <v>81.29310344827586</v>
       </c>
       <c r="C27">
-        <v>91.1206896551724</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="D27">
-        <v>84.65517163836206</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E27">
-        <v>91.1206896551724</v>
+        <v>79.05172413793105</v>
       </c>
       <c r="F27">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="G27">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="H27">
-        <v>79.05172413793102</v>
+        <v>87.75862068965516</v>
       </c>
       <c r="I27">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="J27">
-        <v>81.29310344827586</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="K27">
-        <v>87.75862068965516</v>
+        <v>84.65517241379311</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4758,34 +4758,34 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>78.18965517241378</v>
+        <v>80.17241379310344</v>
       </c>
       <c r="C28">
-        <v>91.1206896551724</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="D28">
-        <v>84.65517163814654</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E28">
-        <v>91.1206896551724</v>
+        <v>77.93103448275862</v>
       </c>
       <c r="F28">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="G28">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="H28">
-        <v>77.93103448275862</v>
+        <v>86.63793103448276</v>
       </c>
       <c r="I28">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="J28">
-        <v>80.17241379310344</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="K28">
-        <v>86.63793103448276</v>
+        <v>84.65517241379311</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4793,34 +4793,34 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>78.18965517241378</v>
+        <v>79.05172413793105</v>
       </c>
       <c r="C29">
-        <v>91.1206896551724</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="D29">
-        <v>83.53448198297414</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E29">
-        <v>90</v>
+        <v>76.81034482758621</v>
       </c>
       <c r="F29">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="G29">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="H29">
-        <v>76.81034482758621</v>
+        <v>85.51724137931035</v>
       </c>
       <c r="I29">
         <v>83.53448275862068</v>
       </c>
       <c r="J29">
-        <v>79.05172413793102</v>
+        <v>90</v>
       </c>
       <c r="K29">
-        <v>85.51724137931033</v>
+        <v>83.53448275862068</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4828,34 +4828,34 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>78.18965517241378</v>
+        <v>77.93103448275862</v>
       </c>
       <c r="C30">
-        <v>91.1206896551724</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="D30">
-        <v>82.41379232780172</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E30">
-        <v>88.87931034482759</v>
+        <v>75.68965517241378</v>
       </c>
       <c r="F30">
-        <v>84.6551724137931</v>
+        <v>84.65517241379311</v>
       </c>
       <c r="G30">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="H30">
-        <v>75.68965517241378</v>
+        <v>84.39655172413794</v>
       </c>
       <c r="I30">
         <v>82.41379310344827</v>
       </c>
       <c r="J30">
-        <v>77.93103448275862</v>
+        <v>88.87931034482759</v>
       </c>
       <c r="K30">
-        <v>84.39655172413794</v>
+        <v>82.41379310344827</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4863,34 +4863,34 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>78.18965517241378</v>
+        <v>76.81034482758621</v>
       </c>
       <c r="C31">
-        <v>91.1206896551724</v>
+        <v>91.12068965517243</v>
       </c>
       <c r="D31">
-        <v>81.29310267262929</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E31">
-        <v>87.75862068965516</v>
+        <v>74.56896551724138</v>
       </c>
       <c r="F31">
         <v>83.53448275862068</v>
       </c>
       <c r="G31">
-        <v>78.18965517241378</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="H31">
-        <v>74.56896551724138</v>
+        <v>83.27586206896552</v>
       </c>
       <c r="I31">
         <v>81.29310344827586</v>
       </c>
       <c r="J31">
-        <v>76.81034482758621</v>
+        <v>87.75862068965516</v>
       </c>
       <c r="K31">
-        <v>83.27586206896552</v>
+        <v>81.29310344827586</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4898,34 +4898,34 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>77.06896551724138</v>
+        <v>75.68965517241378</v>
       </c>
       <c r="C32">
         <v>90</v>
       </c>
       <c r="D32">
-        <v>80.17241301745689</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E32">
-        <v>86.63793103448276</v>
+        <v>73.44827586206897</v>
       </c>
       <c r="F32">
         <v>82.41379310344827</v>
       </c>
       <c r="G32">
-        <v>78.18965517241378</v>
+        <v>77.06896551724138</v>
       </c>
       <c r="H32">
-        <v>73.44827586206897</v>
+        <v>82.1551724137931</v>
       </c>
       <c r="I32">
         <v>80.17241379310344</v>
       </c>
       <c r="J32">
-        <v>75.68965517241378</v>
+        <v>86.63793103448276</v>
       </c>
       <c r="K32">
-        <v>82.1551724137931</v>
+        <v>80.17241379310344</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4933,34 +4933,34 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>75.94827586206897</v>
+        <v>74.56896551724138</v>
       </c>
       <c r="C33">
         <v>88.87931034482759</v>
       </c>
       <c r="D33">
-        <v>79.05172336228448</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E33">
-        <v>85.51724137931033</v>
+        <v>72.32758620689656</v>
       </c>
       <c r="F33">
         <v>81.29310344827586</v>
       </c>
       <c r="G33">
-        <v>78.18965517241378</v>
+        <v>75.94827586206897</v>
       </c>
       <c r="H33">
-        <v>72.32758620689656</v>
+        <v>81.03448275862068</v>
       </c>
       <c r="I33">
-        <v>79.05172413793102</v>
+        <v>79.05172413793105</v>
       </c>
       <c r="J33">
-        <v>74.56896551724138</v>
+        <v>85.51724137931035</v>
       </c>
       <c r="K33">
-        <v>81.03448275862068</v>
+        <v>79.05172413793105</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4968,34 +4968,34 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>74.82758620689654</v>
+        <v>73.44827586206897</v>
       </c>
       <c r="C34">
         <v>87.75862068965516</v>
       </c>
       <c r="D34">
-        <v>77.93103370706895</v>
+        <v>78.18965517241381</v>
       </c>
       <c r="E34">
-        <v>84.39655172413794</v>
+        <v>71.20689655172414</v>
       </c>
       <c r="F34">
         <v>80.17241379310344</v>
       </c>
       <c r="G34">
-        <v>78.18965517241378</v>
+        <v>74.82758620689654</v>
       </c>
       <c r="H34">
-        <v>71.20689655172414</v>
+        <v>79.91379310344828</v>
       </c>
       <c r="I34">
         <v>77.93103448275862</v>
       </c>
       <c r="J34">
-        <v>73.44827586206897</v>
+        <v>84.39655172413794</v>
       </c>
       <c r="K34">
-        <v>79.91379310344827</v>
+        <v>77.93103448275862</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -5003,34 +5003,34 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>73.70689655172414</v>
+        <v>72.32758620689656</v>
       </c>
       <c r="C35">
         <v>86.63793103448276</v>
       </c>
       <c r="D35">
-        <v>76.81034405189655</v>
+        <v>77.06896551724138</v>
       </c>
       <c r="E35">
-        <v>83.27586206896552</v>
+        <v>70.08620689655173</v>
       </c>
       <c r="F35">
-        <v>79.05172413793102</v>
+        <v>79.05172413793105</v>
       </c>
       <c r="G35">
-        <v>77.06896551724138</v>
+        <v>73.70689655172414</v>
       </c>
       <c r="H35">
-        <v>70.08620689655172</v>
+        <v>78.79310344827586</v>
       </c>
       <c r="I35">
         <v>76.81034482758621</v>
       </c>
       <c r="J35">
-        <v>72.32758620689656</v>
+        <v>83.27586206896552</v>
       </c>
       <c r="K35">
-        <v>78.79310344827586</v>
+        <v>76.81034482758621</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -5038,34 +5038,34 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>72.58620689655173</v>
+        <v>71.20689655172414</v>
       </c>
       <c r="C36">
-        <v>85.51724137931033</v>
+        <v>85.51724137931035</v>
       </c>
       <c r="D36">
-        <v>75.68965439672412</v>
+        <v>75.94827586206897</v>
       </c>
       <c r="E36">
-        <v>82.1551724137931</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="F36">
         <v>77.93103448275862</v>
       </c>
       <c r="G36">
-        <v>75.94827586206897</v>
+        <v>72.58620689655173</v>
       </c>
       <c r="H36">
-        <v>68.96551724137932</v>
+        <v>77.67241379310344</v>
       </c>
       <c r="I36">
         <v>75.68965517241378</v>
       </c>
       <c r="J36">
-        <v>71.20689655172414</v>
+        <v>82.1551724137931</v>
       </c>
       <c r="K36">
-        <v>77.67241379310344</v>
+        <v>75.68965517241378</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -5073,34 +5073,34 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>71.46551724137932</v>
+        <v>70.08620689655173</v>
       </c>
       <c r="C37">
         <v>84.39655172413794</v>
       </c>
       <c r="D37">
-        <v>74.56896474155171</v>
+        <v>74.82758620689654</v>
       </c>
       <c r="E37">
-        <v>81.03448275862068</v>
+        <v>67.84482758620689</v>
       </c>
       <c r="F37">
         <v>76.81034482758621</v>
       </c>
       <c r="G37">
-        <v>74.82758620689654</v>
+        <v>71.46551724137932</v>
       </c>
       <c r="H37">
-        <v>67.84482758620689</v>
+        <v>76.55172413793102</v>
       </c>
       <c r="I37">
         <v>74.56896551724138</v>
       </c>
       <c r="J37">
-        <v>70.08620689655172</v>
+        <v>81.03448275862068</v>
       </c>
       <c r="K37">
-        <v>76.55172413793102</v>
+        <v>74.56896551724138</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -5108,34 +5108,34 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>70.34482758620689</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="C38">
         <v>83.27586206896552</v>
       </c>
       <c r="D38">
-        <v>73.4482750863793</v>
+        <v>73.70689655172414</v>
       </c>
       <c r="E38">
-        <v>79.91379310344827</v>
+        <v>66.72413793103448</v>
       </c>
       <c r="F38">
         <v>75.68965517241378</v>
       </c>
       <c r="G38">
-        <v>73.70689655172414</v>
+        <v>70.34482758620689</v>
       </c>
       <c r="H38">
-        <v>66.72413793103448</v>
+        <v>75.43103448275862</v>
       </c>
       <c r="I38">
         <v>73.44827586206897</v>
       </c>
       <c r="J38">
-        <v>68.96551724137932</v>
+        <v>79.91379310344828</v>
       </c>
       <c r="K38">
-        <v>75.43103448275862</v>
+        <v>73.44827586206897</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -5143,34 +5143,34 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>69.22413793103448</v>
+        <v>67.84482758620689</v>
       </c>
       <c r="C39">
         <v>82.1551724137931</v>
       </c>
       <c r="D39">
-        <v>72.32758543120688</v>
+        <v>72.58620689655173</v>
       </c>
       <c r="E39">
-        <v>78.79310344827586</v>
+        <v>65.60344827586206</v>
       </c>
       <c r="F39">
         <v>74.56896551724138</v>
       </c>
       <c r="G39">
-        <v>72.58620689655173</v>
+        <v>69.22413793103448</v>
       </c>
       <c r="H39">
-        <v>65.60344827586206</v>
+        <v>74.31034482758622</v>
       </c>
       <c r="I39">
         <v>72.32758620689656</v>
       </c>
       <c r="J39">
-        <v>67.84482758620689</v>
+        <v>78.79310344827586</v>
       </c>
       <c r="K39">
-        <v>74.31034482758619</v>
+        <v>72.32758620689656</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5178,34 +5178,34 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>68.10344827586206</v>
+        <v>66.72413793103448</v>
       </c>
       <c r="C40">
         <v>81.03448275862068</v>
       </c>
       <c r="D40">
-        <v>71.20689577603447</v>
+        <v>71.46551724137932</v>
       </c>
       <c r="E40">
-        <v>77.67241379310344</v>
+        <v>64.48275862068965</v>
       </c>
       <c r="F40">
         <v>73.44827586206897</v>
       </c>
       <c r="G40">
-        <v>71.46551724137932</v>
+        <v>68.10344827586206</v>
       </c>
       <c r="H40">
-        <v>64.48275862068965</v>
+        <v>73.18965517241379</v>
       </c>
       <c r="I40">
         <v>71.20689655172414</v>
       </c>
       <c r="J40">
-        <v>66.72413793103448</v>
+        <v>77.67241379310344</v>
       </c>
       <c r="K40">
-        <v>73.18965517241379</v>
+        <v>71.20689655172414</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5213,34 +5213,34 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>66.98275862068965</v>
+        <v>65.60344827586206</v>
       </c>
       <c r="C41">
-        <v>79.91379310344827</v>
+        <v>79.91379310344828</v>
       </c>
       <c r="D41">
-        <v>70.08620612083332</v>
+        <v>70.34482758620689</v>
       </c>
       <c r="E41">
-        <v>76.55172413793102</v>
+        <v>63.36206896551724</v>
       </c>
       <c r="F41">
         <v>72.32758620689656</v>
       </c>
       <c r="G41">
-        <v>70.34482758620689</v>
+        <v>66.98275862068965</v>
       </c>
       <c r="H41">
-        <v>63.36206896551724</v>
+        <v>72.06896551724138</v>
       </c>
       <c r="I41">
-        <v>70.08620689655172</v>
+        <v>70.08620689655173</v>
       </c>
       <c r="J41">
-        <v>65.60344827586206</v>
+        <v>76.55172413793102</v>
       </c>
       <c r="K41">
-        <v>72.06896551724138</v>
+        <v>70.08620689655173</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5248,34 +5248,34 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>65.86206896551724</v>
+        <v>64.48275862068965</v>
       </c>
       <c r="C42">
         <v>78.79310344827586</v>
       </c>
       <c r="D42">
-        <v>68.96551646562499</v>
+        <v>69.22413793103448</v>
       </c>
       <c r="E42">
-        <v>75.43103448275862</v>
+        <v>62.24137931034483</v>
       </c>
       <c r="F42">
         <v>71.20689655172414</v>
       </c>
       <c r="G42">
-        <v>69.22413793103448</v>
+        <v>65.86206896551724</v>
       </c>
       <c r="H42">
-        <v>62.24137931034483</v>
+        <v>70.94827586206897</v>
       </c>
       <c r="I42">
         <v>68.96551724137932</v>
       </c>
       <c r="J42">
-        <v>64.48275862068965</v>
+        <v>75.43103448275862</v>
       </c>
       <c r="K42">
-        <v>70.94827586206895</v>
+        <v>68.96551724137932</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5283,34 +5283,34 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>64.74137931034483</v>
+        <v>63.36206896551724</v>
       </c>
       <c r="C43">
         <v>77.67241379310344</v>
       </c>
       <c r="D43">
-        <v>67.8448268104885</v>
+        <v>68.10344827586206</v>
       </c>
       <c r="E43">
-        <v>74.31034482758619</v>
+        <v>61.12068965517241</v>
       </c>
       <c r="F43">
-        <v>70.08620689655172</v>
+        <v>70.08620689655173</v>
       </c>
       <c r="G43">
-        <v>68.10344827586206</v>
+        <v>64.74137931034483</v>
       </c>
       <c r="H43">
-        <v>61.12068965517241</v>
+        <v>69.82758620689656</v>
       </c>
       <c r="I43">
         <v>67.84482758620689</v>
       </c>
       <c r="J43">
-        <v>63.36206896551724</v>
+        <v>74.31034482758622</v>
       </c>
       <c r="K43">
-        <v>69.82758620689656</v>
+        <v>67.84482758620689</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -5318,34 +5318,34 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>63.62068965517241</v>
+        <v>62.24137931034483</v>
       </c>
       <c r="C44">
         <v>76.55172413793102</v>
       </c>
       <c r="D44">
-        <v>66.72413715529557</v>
+        <v>66.98275862068965</v>
       </c>
       <c r="E44">
-        <v>73.18965517241379</v>
+        <v>60</v>
       </c>
       <c r="F44">
         <v>68.96551724137932</v>
       </c>
       <c r="G44">
-        <v>66.98275862068965</v>
+        <v>63.62068965517241</v>
       </c>
       <c r="H44">
-        <v>60</v>
+        <v>68.70689655172414</v>
       </c>
       <c r="I44">
         <v>66.72413793103448</v>
       </c>
       <c r="J44">
-        <v>62.24137931034483</v>
+        <v>73.18965517241379</v>
       </c>
       <c r="K44">
-        <v>68.70689655172414</v>
+        <v>66.72413793103448</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5353,34 +5353,34 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>62.5</v>
+        <v>61.12068965517241</v>
       </c>
       <c r="C45">
         <v>75.43103448275862</v>
       </c>
       <c r="D45">
-        <v>65.60344750014367</v>
+        <v>65.86206896551724</v>
       </c>
       <c r="E45">
-        <v>72.06896551724138</v>
+        <v>58.87931034482759</v>
       </c>
       <c r="F45">
         <v>67.84482758620689</v>
       </c>
       <c r="G45">
-        <v>65.86206896551724</v>
+        <v>62.5</v>
       </c>
       <c r="H45">
-        <v>58.87931034482759</v>
+        <v>67.58620689655173</v>
       </c>
       <c r="I45">
         <v>65.60344827586206</v>
       </c>
       <c r="J45">
-        <v>61.12068965517241</v>
+        <v>72.06896551724138</v>
       </c>
       <c r="K45">
-        <v>67.58620689655173</v>
+        <v>65.60344827586206</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -5388,34 +5388,34 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>61.37931034482759</v>
+        <v>60</v>
       </c>
       <c r="C46">
-        <v>74.31034482758619</v>
+        <v>74.31034482758622</v>
       </c>
       <c r="D46">
-        <v>64.48275784497126</v>
+        <v>64.74137931034483</v>
       </c>
       <c r="E46">
-        <v>70.94827586206895</v>
+        <v>57.75862068965517</v>
       </c>
       <c r="F46">
         <v>66.72413793103448</v>
       </c>
       <c r="G46">
-        <v>64.74137931034483</v>
+        <v>61.37931034482759</v>
       </c>
       <c r="H46">
-        <v>57.75862068965517</v>
+        <v>66.46551724137932</v>
       </c>
       <c r="I46">
         <v>64.48275862068965</v>
       </c>
       <c r="J46">
-        <v>60</v>
+        <v>70.94827586206897</v>
       </c>
       <c r="K46">
-        <v>66.46551724137932</v>
+        <v>64.48275862068965</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -5423,34 +5423,34 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>60.25862068965517</v>
+        <v>58.87931034482759</v>
       </c>
       <c r="C47">
         <v>73.18965517241379</v>
       </c>
       <c r="D47">
-        <v>63.36206818982757</v>
+        <v>63.62068965517241</v>
       </c>
       <c r="E47">
-        <v>69.82758620689656</v>
+        <v>56.63793103448276</v>
       </c>
       <c r="F47">
         <v>65.60344827586206</v>
       </c>
       <c r="G47">
-        <v>63.62068965517241</v>
+        <v>60.25862068965517</v>
       </c>
       <c r="H47">
-        <v>56.63793103448276</v>
+        <v>65.34482758620689</v>
       </c>
       <c r="I47">
         <v>63.36206896551724</v>
       </c>
       <c r="J47">
-        <v>58.87931034482759</v>
+        <v>69.82758620689656</v>
       </c>
       <c r="K47">
-        <v>65.34482758620689</v>
+        <v>63.36206896551724</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5458,34 +5458,34 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>59.13793103448276</v>
+        <v>57.75862068965517</v>
       </c>
       <c r="C48">
         <v>72.06896551724138</v>
       </c>
       <c r="D48">
-        <v>62.24137853465516</v>
+        <v>62.5</v>
       </c>
       <c r="E48">
-        <v>68.70689655172414</v>
+        <v>55.51724137931034</v>
       </c>
       <c r="F48">
         <v>64.48275862068965</v>
       </c>
       <c r="G48">
-        <v>62.5</v>
+        <v>59.13793103448276</v>
       </c>
       <c r="H48">
-        <v>55.51724137931034</v>
+        <v>64.22413793103448</v>
       </c>
       <c r="I48">
         <v>62.24137931034483</v>
       </c>
       <c r="J48">
-        <v>57.75862068965517</v>
+        <v>68.70689655172414</v>
       </c>
       <c r="K48">
-        <v>64.22413793103448</v>
+        <v>62.24137931034483</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -5493,34 +5493,34 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>58.01724137931034</v>
+        <v>56.63793103448276</v>
       </c>
       <c r="C49">
-        <v>70.94827586206895</v>
+        <v>70.94827586206897</v>
       </c>
       <c r="D49">
-        <v>61.12068887945401</v>
+        <v>61.37931034482759</v>
       </c>
       <c r="E49">
-        <v>67.58620689655173</v>
+        <v>54.39655172413793</v>
       </c>
       <c r="F49">
         <v>63.36206896551724</v>
       </c>
       <c r="G49">
-        <v>61.37931034482759</v>
+        <v>58.01724137931034</v>
       </c>
       <c r="H49">
-        <v>54.39655172413793</v>
+        <v>63.10344827586207</v>
       </c>
       <c r="I49">
         <v>61.12068965517241</v>
       </c>
       <c r="J49">
-        <v>56.63793103448276</v>
+        <v>67.58620689655173</v>
       </c>
       <c r="K49">
-        <v>63.10344827586207</v>
+        <v>61.12068965517241</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -5528,34 +5528,34 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>56.89655172413793</v>
+        <v>55.51724137931034</v>
       </c>
       <c r="C50">
         <v>69.82758620689656</v>
       </c>
       <c r="D50">
-        <v>59.99999922426107</v>
+        <v>60.25862068965517</v>
       </c>
       <c r="E50">
-        <v>66.46551724137932</v>
+        <v>53.27586206896552</v>
       </c>
       <c r="F50">
         <v>62.24137931034483</v>
       </c>
       <c r="G50">
-        <v>60.25862068965517</v>
+        <v>56.89655172413793</v>
       </c>
       <c r="H50">
-        <v>53.27586206896552</v>
+        <v>61.98275862068966</v>
       </c>
       <c r="I50">
         <v>60</v>
       </c>
       <c r="J50">
-        <v>55.51724137931034</v>
+        <v>66.46551724137932</v>
       </c>
       <c r="K50">
-        <v>61.98275862068966</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5563,34 +5563,34 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>55.77586206896552</v>
+        <v>54.39655172413793</v>
       </c>
       <c r="C51">
         <v>68.70689655172414</v>
       </c>
       <c r="D51">
-        <v>58.87930956908866</v>
+        <v>59.13793103448276</v>
       </c>
       <c r="E51">
-        <v>65.34482758620689</v>
+        <v>52.1551724137931</v>
       </c>
       <c r="F51">
         <v>61.12068965517241</v>
       </c>
       <c r="G51">
-        <v>59.13793103448276</v>
+        <v>55.77586206896552</v>
       </c>
       <c r="H51">
-        <v>52.1551724137931</v>
+        <v>60.86206896551724</v>
       </c>
       <c r="I51">
         <v>58.87931034482759</v>
       </c>
       <c r="J51">
-        <v>54.39655172413793</v>
+        <v>65.34482758620689</v>
       </c>
       <c r="K51">
-        <v>60.86206896551724</v>
+        <v>58.87931034482759</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -5598,34 +5598,34 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>54.6551724137931</v>
+        <v>53.27586206896552</v>
       </c>
       <c r="C52">
         <v>67.58620689655173</v>
       </c>
       <c r="D52">
-        <v>57.75861991390085</v>
+        <v>58.01724137931034</v>
       </c>
       <c r="E52">
-        <v>64.22413793103448</v>
+        <v>51.03448275862069</v>
       </c>
       <c r="F52">
         <v>60</v>
       </c>
       <c r="G52">
-        <v>58.01724137931034</v>
+        <v>54.6551724137931</v>
       </c>
       <c r="H52">
-        <v>51.03448275862069</v>
+        <v>59.74137931034483</v>
       </c>
       <c r="I52">
         <v>57.75862068965517</v>
       </c>
       <c r="J52">
-        <v>53.27586206896552</v>
+        <v>64.22413793103448</v>
       </c>
       <c r="K52">
-        <v>59.74137931034483</v>
+        <v>57.75862068965517</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5633,34 +5633,34 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>53.53448275862069</v>
+        <v>52.1551724137931</v>
       </c>
       <c r="C53">
         <v>66.46551724137932</v>
       </c>
       <c r="D53">
-        <v>56.63793025871646</v>
+        <v>56.89655172413793</v>
       </c>
       <c r="E53">
-        <v>63.10344827586207</v>
+        <v>49.91379310344828</v>
       </c>
       <c r="F53">
         <v>58.87931034482759</v>
       </c>
       <c r="G53">
-        <v>56.89655172413793</v>
+        <v>53.53448275862069</v>
       </c>
       <c r="H53">
-        <v>49.91379310344828</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="I53">
         <v>56.63793103448276</v>
       </c>
       <c r="J53">
-        <v>52.1551724137931</v>
+        <v>63.10344827586207</v>
       </c>
       <c r="K53">
-        <v>58.62068965517241</v>
+        <v>56.63793103448276</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5668,34 +5668,34 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>52.41379310344828</v>
+        <v>51.03448275862069</v>
       </c>
       <c r="C54">
         <v>65.34482758620689</v>
       </c>
       <c r="D54">
-        <v>55.51724060357143</v>
+        <v>55.77586206896552</v>
       </c>
       <c r="E54">
-        <v>61.98275862068966</v>
+        <v>48.79310344827586</v>
       </c>
       <c r="F54">
         <v>57.75862068965517</v>
       </c>
       <c r="G54">
-        <v>55.77586206896552</v>
+        <v>52.41379310344828</v>
       </c>
       <c r="H54">
-        <v>48.79310344827586</v>
+        <v>57.5</v>
       </c>
       <c r="I54">
         <v>55.51724137931034</v>
       </c>
       <c r="J54">
-        <v>51.03448275862069</v>
+        <v>61.98275862068966</v>
       </c>
       <c r="K54">
-        <v>57.5</v>
+        <v>55.51724137931034</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -5703,34 +5703,34 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>51.29310344827586</v>
+        <v>49.91379310344828</v>
       </c>
       <c r="C55">
         <v>64.22413793103448</v>
       </c>
       <c r="D55">
-        <v>54.39655094839901</v>
+        <v>54.6551724137931</v>
       </c>
       <c r="E55">
-        <v>60.86206896551724</v>
+        <v>47.67241379310344</v>
       </c>
       <c r="F55">
         <v>56.63793103448276</v>
       </c>
       <c r="G55">
-        <v>54.6551724137931</v>
+        <v>51.29310344827586</v>
       </c>
       <c r="H55">
-        <v>47.67241379310344</v>
+        <v>56.37931034482759</v>
       </c>
       <c r="I55">
         <v>54.39655172413793</v>
       </c>
       <c r="J55">
-        <v>49.91379310344828</v>
+        <v>60.86206896551724</v>
       </c>
       <c r="K55">
-        <v>56.37931034482759</v>
+        <v>54.39655172413793</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -5738,34 +5738,34 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>50.17241379310344</v>
+        <v>48.79310344827586</v>
       </c>
       <c r="C56">
         <v>63.10344827586207</v>
       </c>
       <c r="D56">
-        <v>53.27586129319923</v>
+        <v>53.53448275862069</v>
       </c>
       <c r="E56">
-        <v>59.74137931034483</v>
+        <v>46.55172413793103</v>
       </c>
       <c r="F56">
         <v>55.51724137931034</v>
       </c>
       <c r="G56">
-        <v>53.53448275862069</v>
+        <v>50.17241379310344</v>
       </c>
       <c r="H56">
-        <v>46.55172413793103</v>
+        <v>55.25862068965517</v>
       </c>
       <c r="I56">
         <v>53.27586206896552</v>
       </c>
       <c r="J56">
-        <v>48.79310344827586</v>
+        <v>59.74137931034483</v>
       </c>
       <c r="K56">
-        <v>55.25862068965517</v>
+        <v>53.27586206896552</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -5773,34 +5773,34 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>49.05172413793103</v>
+        <v>47.67241379310344</v>
       </c>
       <c r="C57">
         <v>61.98275862068966</v>
       </c>
       <c r="D57">
-        <v>52.15517163810344</v>
+        <v>52.41379310344828</v>
       </c>
       <c r="E57">
-        <v>58.62068965517241</v>
+        <v>45.43103448275862</v>
       </c>
       <c r="F57">
         <v>54.39655172413793</v>
       </c>
       <c r="G57">
-        <v>52.41379310344828</v>
+        <v>49.05172413793103</v>
       </c>
       <c r="H57">
-        <v>45.43103448275862</v>
+        <v>54.13793103448276</v>
       </c>
       <c r="I57">
         <v>52.1551724137931</v>
       </c>
       <c r="J57">
-        <v>47.67241379310344</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="K57">
-        <v>54.13793103448276</v>
+        <v>52.1551724137931</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -5808,34 +5808,34 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>47.93103448275862</v>
+        <v>46.55172413793103</v>
       </c>
       <c r="C58">
         <v>60.86206896551724</v>
       </c>
       <c r="D58">
-        <v>51.03448198288176</v>
+        <v>51.29310344827586</v>
       </c>
       <c r="E58">
-        <v>57.5</v>
+        <v>44.3103448275862</v>
       </c>
       <c r="F58">
         <v>53.27586206896552</v>
       </c>
       <c r="G58">
-        <v>51.29310344827586</v>
+        <v>47.93103448275862</v>
       </c>
       <c r="H58">
-        <v>44.3103448275862</v>
+        <v>53.01724137931034</v>
       </c>
       <c r="I58">
         <v>51.03448275862069</v>
       </c>
       <c r="J58">
-        <v>46.55172413793103</v>
+        <v>57.5</v>
       </c>
       <c r="K58">
-        <v>53.01724137931034</v>
+        <v>51.03448275862069</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -5843,34 +5843,34 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>46.81034482758621</v>
+        <v>45.43103448275862</v>
       </c>
       <c r="C59">
         <v>59.74137931034483</v>
       </c>
       <c r="D59">
-        <v>49.91379232772987</v>
+        <v>50.17241379310344</v>
       </c>
       <c r="E59">
-        <v>56.37931034482759</v>
+        <v>43.1896551724138</v>
       </c>
       <c r="F59">
         <v>52.1551724137931</v>
       </c>
       <c r="G59">
-        <v>50.17241379310344</v>
+        <v>46.81034482758621</v>
       </c>
       <c r="H59">
-        <v>43.18965517241379</v>
+        <v>51.89655172413793</v>
       </c>
       <c r="I59">
         <v>49.91379310344828</v>
       </c>
       <c r="J59">
-        <v>45.43103448275862</v>
+        <v>56.37931034482759</v>
       </c>
       <c r="K59">
-        <v>51.89655172413793</v>
+        <v>49.91379310344828</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -5878,34 +5878,34 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>45.68965517241379</v>
+        <v>44.3103448275862</v>
       </c>
       <c r="C60">
         <v>58.62068965517241</v>
       </c>
       <c r="D60">
-        <v>48.79310267253694</v>
+        <v>49.05172413793103</v>
       </c>
       <c r="E60">
-        <v>55.25862068965517</v>
+        <v>42.06896551724138</v>
       </c>
       <c r="F60">
         <v>51.03448275862069</v>
       </c>
       <c r="G60">
-        <v>49.05172413793103</v>
+        <v>45.68965517241379</v>
       </c>
       <c r="H60">
-        <v>42.06896551724138</v>
+        <v>50.77586206896552</v>
       </c>
       <c r="I60">
         <v>48.79310344827586</v>
       </c>
       <c r="J60">
-        <v>44.3103448275862</v>
+        <v>55.25862068965517</v>
       </c>
       <c r="K60">
-        <v>50.77586206896552</v>
+        <v>48.79310344827586</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -5913,34 +5913,34 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>44.56896551724138</v>
+        <v>43.1896551724138</v>
       </c>
       <c r="C61">
         <v>57.5</v>
       </c>
       <c r="D61">
-        <v>47.67241301741377</v>
+        <v>47.93103448275862</v>
       </c>
       <c r="E61">
-        <v>54.13793103448276</v>
+        <v>40.94827586206897</v>
       </c>
       <c r="F61">
         <v>49.91379310344828</v>
       </c>
       <c r="G61">
-        <v>47.93103448275862</v>
+        <v>44.56896551724138</v>
       </c>
       <c r="H61">
-        <v>40.94827586206897</v>
+        <v>49.6551724137931</v>
       </c>
       <c r="I61">
         <v>47.67241379310344</v>
       </c>
       <c r="J61">
-        <v>43.18965517241379</v>
+        <v>54.13793103448276</v>
       </c>
       <c r="K61">
-        <v>49.6551724137931</v>
+        <v>47.67241379310344</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -5948,34 +5948,34 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>43.44827586206896</v>
+        <v>42.06896551724138</v>
       </c>
       <c r="C62">
         <v>56.37931034482759</v>
       </c>
       <c r="D62">
-        <v>46.55172336224137</v>
+        <v>46.81034482758621</v>
       </c>
       <c r="E62">
-        <v>53.01724137931034</v>
+        <v>39.82758620689656</v>
       </c>
       <c r="F62">
         <v>48.79310344827586</v>
       </c>
       <c r="G62">
-        <v>46.81034482758621</v>
+        <v>43.44827586206896</v>
       </c>
       <c r="H62">
-        <v>39.82758620689656</v>
+        <v>48.53448275862069</v>
       </c>
       <c r="I62">
         <v>46.55172413793103</v>
       </c>
       <c r="J62">
-        <v>42.06896551724138</v>
+        <v>53.01724137931034</v>
       </c>
       <c r="K62">
-        <v>48.53448275862069</v>
+        <v>46.55172413793103</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -5983,34 +5983,34 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>42.32758620689655</v>
+        <v>40.94827586206897</v>
       </c>
       <c r="C63">
         <v>55.25862068965517</v>
       </c>
       <c r="D63">
-        <v>45.4310337070043</v>
+        <v>45.68965517241379</v>
       </c>
       <c r="E63">
-        <v>51.89655172413793</v>
+        <v>38.70689655172414</v>
       </c>
       <c r="F63">
         <v>47.67241379310344</v>
       </c>
       <c r="G63">
-        <v>45.68965517241379</v>
+        <v>42.32758620689656</v>
       </c>
       <c r="H63">
-        <v>38.70689655172414</v>
+        <v>47.41379310344828</v>
       </c>
       <c r="I63">
         <v>45.43103448275862</v>
       </c>
       <c r="J63">
-        <v>40.94827586206897</v>
+        <v>51.89655172413793</v>
       </c>
       <c r="K63">
-        <v>47.41379310344828</v>
+        <v>45.43103448275862</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -6018,34 +6018,34 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>41.20689655172414</v>
+        <v>39.82758620689656</v>
       </c>
       <c r="C64">
         <v>54.13793103448276</v>
       </c>
       <c r="D64">
-        <v>44.3103440518319</v>
+        <v>44.56896551724138</v>
       </c>
       <c r="E64">
-        <v>50.77586206896552</v>
+        <v>37.58620689655173</v>
       </c>
       <c r="F64">
         <v>46.55172413793103</v>
       </c>
       <c r="G64">
-        <v>44.56896551724138</v>
+        <v>41.20689655172414</v>
       </c>
       <c r="H64">
-        <v>37.58620689655172</v>
+        <v>46.29310344827586</v>
       </c>
       <c r="I64">
         <v>44.3103448275862</v>
       </c>
       <c r="J64">
-        <v>39.82758620689656</v>
+        <v>50.77586206896552</v>
       </c>
       <c r="K64">
-        <v>46.29310344827586</v>
+        <v>44.3103448275862</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -6053,34 +6053,34 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>40.08620689655172</v>
+        <v>38.70689655172414</v>
       </c>
       <c r="C65">
         <v>53.01724137931034</v>
       </c>
       <c r="D65">
-        <v>43.18965439672414</v>
+        <v>43.44827586206896</v>
       </c>
       <c r="E65">
-        <v>49.6551724137931</v>
+        <v>36.46551724137931</v>
       </c>
       <c r="F65">
         <v>45.43103448275862</v>
       </c>
       <c r="G65">
-        <v>43.44827586206896</v>
+        <v>40.08620689655172</v>
       </c>
       <c r="H65">
-        <v>36.46551724137931</v>
+        <v>45.17241379310344</v>
       </c>
       <c r="I65">
-        <v>43.18965517241379</v>
+        <v>43.1896551724138</v>
       </c>
       <c r="J65">
-        <v>38.70689655172414</v>
+        <v>49.6551724137931</v>
       </c>
       <c r="K65">
-        <v>45.17241379310344</v>
+        <v>43.1896551724138</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -6088,34 +6088,34 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>38.96551724137931</v>
+        <v>37.58620689655173</v>
       </c>
       <c r="C66">
         <v>51.89655172413793</v>
       </c>
       <c r="D66">
-        <v>42.06896474155172</v>
+        <v>42.32758620689656</v>
       </c>
       <c r="E66">
-        <v>48.53448275862069</v>
+        <v>35.3448275862069</v>
       </c>
       <c r="F66">
         <v>44.3103448275862</v>
       </c>
       <c r="G66">
-        <v>42.32758620689655</v>
+        <v>38.96551724137931</v>
       </c>
       <c r="H66">
-        <v>35.3448275862069</v>
+        <v>44.05172413793104</v>
       </c>
       <c r="I66">
         <v>42.06896551724138</v>
       </c>
       <c r="J66">
-        <v>37.58620689655172</v>
+        <v>48.53448275862069</v>
       </c>
       <c r="K66">
-        <v>44.05172413793103</v>
+        <v>42.06896551724138</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -6123,34 +6123,34 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>37.84482758620689</v>
+        <v>36.46551724137931</v>
       </c>
       <c r="C67">
         <v>50.77586206896552</v>
       </c>
       <c r="D67">
-        <v>40.94827508637931</v>
+        <v>41.20689655172414</v>
       </c>
       <c r="E67">
-        <v>47.41379310344828</v>
+        <v>34.22413793103448</v>
       </c>
       <c r="F67">
-        <v>43.18965517241379</v>
+        <v>43.1896551724138</v>
       </c>
       <c r="G67">
-        <v>41.20689655172414</v>
+        <v>37.84482758620689</v>
       </c>
       <c r="H67">
-        <v>34.22413793103448</v>
+        <v>42.93103448275862</v>
       </c>
       <c r="I67">
         <v>40.94827586206897</v>
       </c>
       <c r="J67">
-        <v>36.46551724137931</v>
+        <v>47.41379310344828</v>
       </c>
       <c r="K67">
-        <v>42.93103448275862</v>
+        <v>40.94827586206897</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -6158,34 +6158,34 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>36.72413793103448</v>
+        <v>35.3448275862069</v>
       </c>
       <c r="C68">
         <v>49.6551724137931</v>
       </c>
       <c r="D68">
-        <v>39.82758543120689</v>
+        <v>40.08620689655172</v>
       </c>
       <c r="E68">
-        <v>46.29310344827586</v>
+        <v>33.10344827586207</v>
       </c>
       <c r="F68">
         <v>42.06896551724138</v>
       </c>
       <c r="G68">
-        <v>40.08620689655172</v>
+        <v>36.72413793103448</v>
       </c>
       <c r="H68">
-        <v>33.10344827586206</v>
+        <v>41.81034482758621</v>
       </c>
       <c r="I68">
         <v>39.82758620689656</v>
       </c>
       <c r="J68">
-        <v>35.3448275862069</v>
+        <v>46.29310344827586</v>
       </c>
       <c r="K68">
-        <v>41.81034482758621</v>
+        <v>39.82758620689656</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -6193,34 +6193,34 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>35.60344827586207</v>
+        <v>34.22413793103448</v>
       </c>
       <c r="C69">
         <v>48.53448275862069</v>
       </c>
       <c r="D69">
-        <v>38.70689577600574</v>
+        <v>38.96551724137931</v>
       </c>
       <c r="E69">
-        <v>45.17241379310344</v>
+        <v>31.98275862068965</v>
       </c>
       <c r="F69">
         <v>40.94827586206897</v>
       </c>
       <c r="G69">
-        <v>38.96551724137931</v>
+        <v>35.60344827586207</v>
       </c>
       <c r="H69">
-        <v>31.98275862068965</v>
+        <v>40.68965517241379</v>
       </c>
       <c r="I69">
         <v>38.70689655172414</v>
       </c>
       <c r="J69">
-        <v>34.22413793103448</v>
+        <v>45.17241379310344</v>
       </c>
       <c r="K69">
-        <v>40.68965517241379</v>
+        <v>38.70689655172414</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -6228,34 +6228,34 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>34.48275862068966</v>
+        <v>33.10344827586207</v>
       </c>
       <c r="C70">
         <v>47.41379310344828</v>
       </c>
       <c r="D70">
-        <v>37.58620612083333</v>
+        <v>37.84482758620689</v>
       </c>
       <c r="E70">
-        <v>44.05172413793103</v>
+        <v>30.86206896551724</v>
       </c>
       <c r="F70">
         <v>39.82758620689656</v>
       </c>
       <c r="G70">
-        <v>37.84482758620689</v>
+        <v>34.48275862068966</v>
       </c>
       <c r="H70">
-        <v>30.86206896551724</v>
+        <v>39.56896551724137</v>
       </c>
       <c r="I70">
-        <v>37.58620689655172</v>
+        <v>37.58620689655173</v>
       </c>
       <c r="J70">
-        <v>33.10344827586206</v>
+        <v>44.05172413793104</v>
       </c>
       <c r="K70">
-        <v>39.56896551724137</v>
+        <v>37.58620689655173</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -6263,34 +6263,34 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>33.36206896551724</v>
+        <v>31.98275862068965</v>
       </c>
       <c r="C71">
         <v>46.29310344827586</v>
       </c>
       <c r="D71">
-        <v>36.46551646568965</v>
+        <v>36.72413793103448</v>
       </c>
       <c r="E71">
-        <v>42.93103448275862</v>
+        <v>29.74137931034483</v>
       </c>
       <c r="F71">
         <v>38.70689655172414</v>
       </c>
       <c r="G71">
-        <v>36.72413793103448</v>
+        <v>33.36206896551724</v>
       </c>
       <c r="H71">
-        <v>29.74137931034483</v>
+        <v>38.44827586206897</v>
       </c>
       <c r="I71">
         <v>36.46551724137931</v>
       </c>
       <c r="J71">
-        <v>31.98275862068965</v>
+        <v>42.93103448275862</v>
       </c>
       <c r="K71">
-        <v>38.44827586206896</v>
+        <v>36.46551724137931</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -6298,34 +6298,34 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>32.24137931034483</v>
+        <v>30.86206896551724</v>
       </c>
       <c r="C72">
         <v>45.17241379310344</v>
       </c>
       <c r="D72">
-        <v>35.3448268104885</v>
+        <v>35.60344827586207</v>
       </c>
       <c r="E72">
-        <v>41.81034482758621</v>
+        <v>28.62068965517241</v>
       </c>
       <c r="F72">
-        <v>37.58620689655172</v>
+        <v>37.58620689655173</v>
       </c>
       <c r="G72">
-        <v>35.60344827586207</v>
+        <v>32.24137931034483</v>
       </c>
       <c r="H72">
-        <v>28.62068965517241</v>
+        <v>37.32758620689656</v>
       </c>
       <c r="I72">
         <v>35.3448275862069</v>
       </c>
       <c r="J72">
-        <v>30.86206896551724</v>
+        <v>41.81034482758621</v>
       </c>
       <c r="K72">
-        <v>37.32758620689656</v>
+        <v>35.3448275862069</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -6333,34 +6333,34 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>31.12068965517241</v>
+        <v>29.74137931034483</v>
       </c>
       <c r="C73">
-        <v>44.05172413793103</v>
+        <v>44.05172413793104</v>
       </c>
       <c r="D73">
-        <v>34.22413715534483</v>
+        <v>34.48275862068966</v>
       </c>
       <c r="E73">
-        <v>40.68965517241379</v>
+        <v>27.5</v>
       </c>
       <c r="F73">
         <v>36.46551724137931</v>
       </c>
       <c r="G73">
-        <v>34.48275862068966</v>
+        <v>31.12068965517241</v>
       </c>
       <c r="H73">
-        <v>27.5</v>
+        <v>36.20689655172414</v>
       </c>
       <c r="I73">
         <v>34.22413793103448</v>
       </c>
       <c r="J73">
-        <v>29.74137931034483</v>
+        <v>40.68965517241379</v>
       </c>
       <c r="K73">
-        <v>36.20689655172414</v>
+        <v>34.22413793103448</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -6368,34 +6368,34 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>30</v>
+        <v>28.62068965517241</v>
       </c>
       <c r="C74">
         <v>42.93103448275862</v>
       </c>
       <c r="D74">
-        <v>33.10344750017241</v>
+        <v>33.36206896551724</v>
       </c>
       <c r="E74">
-        <v>39.56896551724137</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="F74">
         <v>35.3448275862069</v>
       </c>
       <c r="G74">
-        <v>33.36206896551724</v>
+        <v>30</v>
       </c>
       <c r="H74">
-        <v>26.37931034482759</v>
+        <v>35.08620689655172</v>
       </c>
       <c r="I74">
-        <v>33.10344827586206</v>
+        <v>33.10344827586207</v>
       </c>
       <c r="J74">
-        <v>28.62068965517241</v>
+        <v>39.56896551724137</v>
       </c>
       <c r="K74">
-        <v>35.08620689655172</v>
+        <v>33.10344827586207</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -6403,34 +6403,34 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>28.87931034482759</v>
+        <v>27.5</v>
       </c>
       <c r="C75">
         <v>41.81034482758621</v>
       </c>
       <c r="D75">
-        <v>31.982757845</v>
+        <v>32.24137931034483</v>
       </c>
       <c r="E75">
-        <v>38.44827586206896</v>
+        <v>25.25862068965517</v>
       </c>
       <c r="F75">
         <v>34.22413793103448</v>
       </c>
       <c r="G75">
-        <v>32.24137931034483</v>
+        <v>28.87931034482759</v>
       </c>
       <c r="H75">
-        <v>25.25862068965517</v>
+        <v>33.96551724137931</v>
       </c>
       <c r="I75">
         <v>31.98275862068965</v>
       </c>
       <c r="J75">
-        <v>27.5</v>
+        <v>38.44827586206897</v>
       </c>
       <c r="K75">
-        <v>33.9655172413793</v>
+        <v>31.98275862068965</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6438,34 +6438,34 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>27.75862068965517</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C76">
         <v>40.68965517241379</v>
       </c>
       <c r="D76">
-        <v>30.86206818982758</v>
+        <v>31.12068965517241</v>
       </c>
       <c r="E76">
-        <v>37.32758620689656</v>
+        <v>24.13793103448276</v>
       </c>
       <c r="F76">
-        <v>33.10344827586206</v>
+        <v>33.10344827586207</v>
       </c>
       <c r="G76">
-        <v>31.12068965517241</v>
+        <v>27.75862068965517</v>
       </c>
       <c r="H76">
-        <v>24.13793103448276</v>
+        <v>32.8448275862069</v>
       </c>
       <c r="I76">
         <v>30.86206896551724</v>
       </c>
       <c r="J76">
-        <v>26.37931034482759</v>
+        <v>37.32758620689656</v>
       </c>
       <c r="K76">
-        <v>32.8448275862069</v>
+        <v>30.86206896551724</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -6473,34 +6473,34 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>26.63793103448276</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C77">
         <v>39.56896551724137</v>
       </c>
       <c r="D77">
-        <v>29.74137853465517</v>
+        <v>30</v>
       </c>
       <c r="E77">
-        <v>36.20689655172414</v>
+        <v>23.01724137931034</v>
       </c>
       <c r="F77">
         <v>31.98275862068965</v>
       </c>
       <c r="G77">
-        <v>30</v>
+        <v>26.63793103448276</v>
       </c>
       <c r="H77">
-        <v>23.01724137931034</v>
+        <v>31.72413793103448</v>
       </c>
       <c r="I77">
         <v>29.74137931034483</v>
       </c>
       <c r="J77">
-        <v>26.37931034482759</v>
+        <v>36.20689655172414</v>
       </c>
       <c r="K77">
-        <v>31.72413793103448</v>
+        <v>29.74137931034483</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -6508,34 +6508,34 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>25.51724137931035</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C78">
-        <v>38.44827586206896</v>
+        <v>38.44827586206897</v>
       </c>
       <c r="D78">
-        <v>28.62068887948276</v>
+        <v>28.87931034482759</v>
       </c>
       <c r="E78">
-        <v>35.08620689655172</v>
+        <v>21.89655172413793</v>
       </c>
       <c r="F78">
         <v>30.86206896551724</v>
       </c>
       <c r="G78">
-        <v>28.87931034482759</v>
+        <v>25.51724137931035</v>
       </c>
       <c r="H78">
-        <v>21.89655172413793</v>
+        <v>30.60344827586207</v>
       </c>
       <c r="I78">
         <v>28.62068965517241</v>
       </c>
       <c r="J78">
-        <v>26.37931034482759</v>
+        <v>35.08620689655172</v>
       </c>
       <c r="K78">
-        <v>30.60344827586207</v>
+        <v>28.62068965517241</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -6543,34 +6543,34 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C79">
         <v>37.32758620689656</v>
       </c>
       <c r="D79">
-        <v>27.49999922431035</v>
+        <v>27.75862068965517</v>
       </c>
       <c r="E79">
-        <v>33.9655172413793</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F79">
         <v>29.74137931034483</v>
       </c>
       <c r="G79">
-        <v>27.75862068965517</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H79">
-        <v>20.77586206896552</v>
+        <v>29.48275862068965</v>
       </c>
       <c r="I79">
         <v>27.5</v>
       </c>
       <c r="J79">
-        <v>26.37931034482759</v>
+        <v>33.96551724137931</v>
       </c>
       <c r="K79">
-        <v>29.48275862068965</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -6578,34 +6578,34 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C80">
         <v>36.20689655172414</v>
       </c>
       <c r="D80">
-        <v>26.37930956913793</v>
+        <v>26.63793103448276</v>
       </c>
       <c r="E80">
-        <v>32.8448275862069</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F80">
         <v>28.62068965517241</v>
       </c>
       <c r="G80">
-        <v>26.63793103448276</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H80">
-        <v>20.77586206896552</v>
+        <v>28.36206896551724</v>
       </c>
       <c r="I80">
         <v>26.37931034482759</v>
       </c>
       <c r="J80">
+        <v>32.8448275862069</v>
+      </c>
+      <c r="K80">
         <v>26.37931034482759</v>
-      </c>
-      <c r="K80">
-        <v>28.36206896551724</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -6613,34 +6613,34 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C81">
         <v>35.08620689655172</v>
       </c>
       <c r="D81">
-        <v>25.25861991396551</v>
+        <v>25.51724137931035</v>
       </c>
       <c r="E81">
-        <v>31.72413793103448</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F81">
         <v>27.5</v>
       </c>
       <c r="G81">
-        <v>25.51724137931035</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H81">
-        <v>20.77586206896552</v>
+        <v>27.24137931034483</v>
       </c>
       <c r="I81">
         <v>25.25862068965517</v>
       </c>
       <c r="J81">
-        <v>26.37931034482759</v>
+        <v>31.72413793103448</v>
       </c>
       <c r="K81">
-        <v>27.24137931034483</v>
+        <v>25.25862068965517</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -6648,16 +6648,16 @@
         <v>81</v>
       </c>
       <c r="B82">
+        <v>26.37931034482759</v>
+      </c>
+      <c r="C82">
+        <v>33.96551724137931</v>
+      </c>
+      <c r="D82">
         <v>24.39655172413793</v>
       </c>
-      <c r="C82">
-        <v>33.9655172413793</v>
-      </c>
-      <c r="D82">
-        <v>24.13793025879311</v>
-      </c>
       <c r="E82">
-        <v>30.60344827586207</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F82">
         <v>26.37931034482759</v>
@@ -6666,16 +6666,16 @@
         <v>24.39655172413793</v>
       </c>
       <c r="H82">
-        <v>20.77586206896552</v>
+        <v>26.12068965517241</v>
       </c>
       <c r="I82">
         <v>24.13793103448276</v>
       </c>
       <c r="J82">
-        <v>26.37931034482759</v>
+        <v>30.60344827586207</v>
       </c>
       <c r="K82">
-        <v>26.12068965517241</v>
+        <v>24.13793103448276</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -6683,34 +6683,34 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C83">
         <v>32.8448275862069</v>
       </c>
       <c r="D83">
-        <v>23.01724060362069</v>
+        <v>23.27586206896552</v>
       </c>
       <c r="E83">
-        <v>29.48275862068965</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F83">
         <v>25.25862068965517</v>
       </c>
       <c r="G83">
-        <v>23.27586206896552</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H83">
-        <v>20.77586206896552</v>
+        <v>25</v>
       </c>
       <c r="I83">
         <v>23.01724137931034</v>
       </c>
       <c r="J83">
-        <v>26.37931034482759</v>
+        <v>29.48275862068965</v>
       </c>
       <c r="K83">
-        <v>25</v>
+        <v>23.01724137931034</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -6718,34 +6718,34 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C84">
         <v>31.72413793103448</v>
       </c>
       <c r="D84">
-        <v>21.89655094849138</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E84">
-        <v>28.36206896551724</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F84">
         <v>24.13793103448276</v>
       </c>
       <c r="G84">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H84">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I84">
         <v>21.89655172413793</v>
       </c>
       <c r="J84">
-        <v>26.37931034482759</v>
+        <v>28.36206896551724</v>
       </c>
       <c r="K84">
-        <v>23.87931034482759</v>
+        <v>21.89655172413793</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -6753,34 +6753,34 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C85">
         <v>30.60344827586207</v>
       </c>
       <c r="D85">
-        <v>20.77586129353448</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E85">
-        <v>27.24137931034483</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F85">
         <v>23.01724137931034</v>
       </c>
       <c r="G85">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H85">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I85">
         <v>20.77586206896552</v>
       </c>
       <c r="J85">
-        <v>26.37931034482759</v>
+        <v>27.24137931034483</v>
       </c>
       <c r="K85">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -6788,34 +6788,34 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C86">
         <v>29.48275862068965</v>
       </c>
       <c r="D86">
-        <v>20.77586129353448</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E86">
-        <v>26.12068965517241</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F86">
         <v>23.01724137931034</v>
       </c>
       <c r="G86">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H86">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I86">
         <v>20.77586206896552</v>
       </c>
       <c r="J86">
-        <v>26.37931034482759</v>
+        <v>26.12068965517241</v>
       </c>
       <c r="K86">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -6823,34 +6823,34 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C87">
         <v>28.36206896551724</v>
       </c>
       <c r="D87">
-        <v>20.77586129353448</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E87">
-        <v>25</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F87">
         <v>23.01724137931034</v>
       </c>
       <c r="G87">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H87">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I87">
         <v>20.77586206896552</v>
       </c>
       <c r="J87">
-        <v>26.37931034482759</v>
+        <v>25</v>
       </c>
       <c r="K87">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -6858,34 +6858,34 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C88">
         <v>27.24137931034483</v>
       </c>
       <c r="D88">
-        <v>20.77586129353448</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E88">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F88">
         <v>23.01724137931034</v>
       </c>
       <c r="G88">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H88">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I88">
         <v>20.77586206896552</v>
       </c>
       <c r="J88">
-        <v>26.37931034482759</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="K88">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -6893,34 +6893,34 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C89">
         <v>26.12068965517241</v>
       </c>
       <c r="D89">
-        <v>20.77586129353448</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E89">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F89">
         <v>23.01724137931034</v>
       </c>
       <c r="G89">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H89">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I89">
         <v>20.77586206896552</v>
       </c>
       <c r="J89">
-        <v>26.37931034482759</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="K89">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -6928,34 +6928,34 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C90">
         <v>25</v>
       </c>
       <c r="D90">
-        <v>20.77586129353448</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E90">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F90">
         <v>23.01724137931034</v>
       </c>
       <c r="G90">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H90">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I90">
         <v>20.77586206896552</v>
       </c>
       <c r="J90">
-        <v>26.37931034482759</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="K90">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -6963,34 +6963,34 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C91">
         <v>23.87931034482759</v>
       </c>
       <c r="D91">
-        <v>20.77586129396552</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E91">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F91">
         <v>23.01724137931034</v>
       </c>
       <c r="G91">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H91">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I91">
         <v>20.77586206896552</v>
       </c>
       <c r="J91">
-        <v>26.37931034482759</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="K91">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -6998,34 +6998,34 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C92">
         <v>23.87931034482759</v>
       </c>
       <c r="D92">
-        <v>20.77586129396552</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E92">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F92">
         <v>23.01724137931034</v>
       </c>
       <c r="G92">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H92">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I92">
         <v>20.77586206896552</v>
       </c>
       <c r="J92">
-        <v>26.37931034482759</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="K92">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -7033,34 +7033,34 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C93">
         <v>23.87931034482759</v>
       </c>
       <c r="D93">
-        <v>20.77586129396552</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E93">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F93">
         <v>23.01724137931034</v>
       </c>
       <c r="G93">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H93">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I93">
         <v>20.77586206896552</v>
       </c>
       <c r="J93">
-        <v>26.37931034482759</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="K93">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -7068,34 +7068,34 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C94">
         <v>23.87931034482759</v>
       </c>
       <c r="D94">
-        <v>20.77586129396552</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E94">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F94">
         <v>23.01724137931034</v>
       </c>
       <c r="G94">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H94">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I94">
         <v>20.77586206896552</v>
       </c>
       <c r="J94">
-        <v>26.37931034482759</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="K94">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -7103,34 +7103,34 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C95">
         <v>23.87931034482759</v>
       </c>
       <c r="D95">
-        <v>20.77586129396552</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E95">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F95">
         <v>23.01724137931034</v>
       </c>
       <c r="G95">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H95">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I95">
         <v>20.77586206896552</v>
       </c>
       <c r="J95">
-        <v>26.37931034482759</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="K95">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -7138,34 +7138,34 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C96">
         <v>23.87931034482759</v>
       </c>
       <c r="D96">
-        <v>20.77586129396552</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E96">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F96">
         <v>23.01724137931034</v>
       </c>
       <c r="G96">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H96">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I96">
         <v>20.77586206896552</v>
       </c>
       <c r="J96">
-        <v>26.37931034482759</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="K96">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -7173,34 +7173,34 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>24.39655172413793</v>
+        <v>26.37931034482759</v>
       </c>
       <c r="C97">
         <v>23.87931034482759</v>
       </c>
       <c r="D97">
-        <v>20.77586129396552</v>
+        <v>22.1551724137931</v>
       </c>
       <c r="E97">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
       <c r="F97">
         <v>23.01724137931034</v>
       </c>
       <c r="G97">
-        <v>22.1551724137931</v>
+        <v>24.39655172413793</v>
       </c>
       <c r="H97">
-        <v>20.77586206896552</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="I97">
         <v>20.77586206896552</v>
       </c>
       <c r="J97">
-        <v>26.37931034482759</v>
+        <v>23.87931034482759</v>
       </c>
       <c r="K97">
-        <v>23.87931034482759</v>
+        <v>20.77586206896552</v>
       </c>
     </row>
   </sheetData>
@@ -7231,7 +7231,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7239,7 +7239,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7247,7 +7247,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7255,7 +7255,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7263,7 +7263,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7271,7 +7271,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7279,7 +7279,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7295,7 +7295,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7311,7 +7311,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7383,7 +7383,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>810</v>
+        <v>540</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -7391,7 +7391,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>449.9999892025843</v>
+        <v>720</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -7399,7 +7399,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>450</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -7407,7 +7407,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>90</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -7415,7 +7415,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -7423,7 +7423,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -7431,7 +7431,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -7439,7 +7439,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -7447,7 +7447,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -7455,7 +7455,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -7463,7 +7463,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7471,7 +7471,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -7479,7 +7479,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -7487,7 +7487,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7495,7 +7495,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -7503,7 +7503,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7511,7 +7511,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7519,7 +7519,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7527,7 +7527,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7535,7 +7535,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -7799,7 +7799,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7807,7 +7807,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -7815,7 +7815,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -7823,7 +7823,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -7831,7 +7831,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -7839,7 +7839,7 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -7847,7 +7847,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -7855,7 +7855,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -7863,7 +7863,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7871,7 +7871,7 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -7879,7 +7879,7 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -7887,7 +7887,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -7895,7 +7895,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -7903,7 +7903,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -7911,7 +7911,7 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -7919,7 +7919,7 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -7927,7 +7927,7 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -7935,7 +7935,7 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:2">
